--- a/kronshtatsky/заказ-наряды ексель/2_НАРЯД_ЗАКАЗЫ_МУСА (1).xlsx
+++ b/kronshtatsky/заказ-наряды ексель/2_НАРЯД_ЗАКАЗЫ_МУСА (1).xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linux\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linux\Documents\schools\kronshtatsky\заказ-наряды ексель\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="18324" windowHeight="10116" firstSheet="4" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12312" windowHeight="9588"/>
   </bookViews>
   <sheets>
     <sheet name="Наряд заказы" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,10 @@
     <sheet name="СКБ_Ст_Ус_ГВЛВ" sheetId="16" r:id="rId12"/>
     <sheet name="РАЗНОЕ_ЗАКРЫТИЕ" sheetId="17" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Наряд заказы'!$F$3:$I$628</definedName>
+  </definedNames>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1425,7 +1428,18 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -1748,6 +1762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:IJ630"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -1757,6 +1772,7 @@
     <col min="4" max="4" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="38.109375" customWidth="1"/>
     <col min="7" max="7" width="52.21875" customWidth="1"/>
+    <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" customWidth="1"/>
     <col min="10" max="10" width="15.33203125" customWidth="1"/>
     <col min="11" max="11" width="21.88671875" customWidth="1"/>
@@ -1825,7 +1841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="39.6">
+    <row r="4" spans="1:12" ht="39.6" hidden="1">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1862,7 +1878,7 @@
       </c>
       <c r="L4" s="9"/>
     </row>
-    <row r="5" spans="1:12" ht="39.6">
+    <row r="5" spans="1:12" ht="39.6" hidden="1">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1899,7 +1915,7 @@
       </c>
       <c r="L5" s="9"/>
     </row>
-    <row r="6" spans="1:12" ht="39.6">
+    <row r="6" spans="1:12" ht="39.6" hidden="1">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1936,7 +1952,7 @@
       </c>
       <c r="L6" s="9"/>
     </row>
-    <row r="7" spans="1:12" ht="39.6">
+    <row r="7" spans="1:12" ht="39.6" hidden="1">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -1973,7 +1989,7 @@
       </c>
       <c r="L7" s="9"/>
     </row>
-    <row r="8" spans="1:12" ht="39.6">
+    <row r="8" spans="1:12" ht="39.6" hidden="1">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -2008,7 +2024,7 @@
       </c>
       <c r="L8" s="9"/>
     </row>
-    <row r="9" spans="1:12" ht="39.6">
+    <row r="9" spans="1:12" ht="39.6" hidden="1">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -2045,7 +2061,7 @@
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="66">
+    <row r="10" spans="1:12" ht="66" hidden="1">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -2082,7 +2098,7 @@
       </c>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:12" ht="66">
+    <row r="11" spans="1:12" ht="66" hidden="1">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -2119,7 +2135,7 @@
       </c>
       <c r="L11" s="9"/>
     </row>
-    <row r="12" spans="1:12" ht="39.6">
+    <row r="12" spans="1:12" ht="39.6" hidden="1">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -2156,7 +2172,7 @@
       </c>
       <c r="L12" s="9"/>
     </row>
-    <row r="13" spans="1:12" ht="39.6">
+    <row r="13" spans="1:12" ht="39.6" hidden="1">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -2193,7 +2209,7 @@
       </c>
       <c r="L13" s="9"/>
     </row>
-    <row r="14" spans="1:12" ht="39.6">
+    <row r="14" spans="1:12" ht="39.6" hidden="1">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -2230,7 +2246,7 @@
       </c>
       <c r="L14" s="9"/>
     </row>
-    <row r="15" spans="1:12" ht="39.6">
+    <row r="15" spans="1:12" ht="39.6" hidden="1">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -2267,7 +2283,7 @@
       </c>
       <c r="L15" s="9"/>
     </row>
-    <row r="16" spans="1:12" ht="39.6">
+    <row r="16" spans="1:12" ht="39.6" hidden="1">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -2304,7 +2320,7 @@
       </c>
       <c r="L16" s="9"/>
     </row>
-    <row r="17" spans="1:12" ht="39.6">
+    <row r="17" spans="1:12" ht="39.6" hidden="1">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -2341,7 +2357,7 @@
       </c>
       <c r="L17" s="9"/>
     </row>
-    <row r="18" spans="1:12" ht="52.8">
+    <row r="18" spans="1:12" ht="52.8" hidden="1">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -2378,7 +2394,7 @@
       </c>
       <c r="L18" s="9"/>
     </row>
-    <row r="19" spans="1:12" ht="27.6">
+    <row r="19" spans="1:12" ht="27.6" hidden="1">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -2415,7 +2431,7 @@
       </c>
       <c r="L19" s="9"/>
     </row>
-    <row r="20" spans="1:12" ht="46.8">
+    <row r="20" spans="1:12" ht="46.8" hidden="1">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -2452,7 +2468,7 @@
       </c>
       <c r="L20" s="9"/>
     </row>
-    <row r="21" spans="1:12" ht="15.6">
+    <row r="21" spans="1:12" ht="15.6" hidden="1">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -2489,7 +2505,7 @@
       </c>
       <c r="L21" s="9"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" hidden="1">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -2526,7 +2542,7 @@
       </c>
       <c r="L22" s="9"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" hidden="1">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -2563,7 +2579,7 @@
       </c>
       <c r="L23" s="9"/>
     </row>
-    <row r="24" spans="1:12" ht="39.6">
+    <row r="24" spans="1:12" ht="39.6" hidden="1">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -2600,7 +2616,7 @@
       </c>
       <c r="L24" s="9"/>
     </row>
-    <row r="25" spans="1:12" ht="52.8">
+    <row r="25" spans="1:12" ht="52.8" hidden="1">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -2637,26 +2653,26 @@
       </c>
       <c r="L25" s="9"/>
     </row>
-    <row r="26" spans="1:12" ht="31.8" customHeight="1">
+    <row r="26" spans="1:12" ht="31.8" hidden="1" customHeight="1">
       <c r="A26" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="119"/>
-      <c r="C26" s="120"/>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="120"/>
-      <c r="I26" s="120"/>
-      <c r="J26" s="121"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="66"/>
       <c r="K26" s="42">
         <f>SUM(K4:K25)</f>
         <v>594110.5</v>
       </c>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" hidden="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2670,7 +2686,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:12" ht="46.2" customHeight="1">
+    <row r="28" spans="1:12" ht="46.2" hidden="1" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>11</v>
       </c>
@@ -2708,7 +2724,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="26.4">
+    <row r="29" spans="1:12" ht="26.4" hidden="1">
       <c r="A29" s="4">
         <v>1</v>
       </c>
@@ -2745,7 +2761,7 @@
       </c>
       <c r="L29" s="8"/>
     </row>
-    <row r="30" spans="1:12" ht="26.4">
+    <row r="30" spans="1:12" ht="26.4" hidden="1">
       <c r="A30" s="4">
         <v>1</v>
       </c>
@@ -2782,7 +2798,7 @@
       </c>
       <c r="L30" s="8"/>
     </row>
-    <row r="31" spans="1:12" ht="26.4">
+    <row r="31" spans="1:12" ht="26.4" hidden="1">
       <c r="A31" s="4">
         <v>1</v>
       </c>
@@ -2819,7 +2835,7 @@
       </c>
       <c r="L31" s="8"/>
     </row>
-    <row r="32" spans="1:12" ht="26.4">
+    <row r="32" spans="1:12" ht="26.4" hidden="1">
       <c r="A32" s="4">
         <v>1</v>
       </c>
@@ -2856,7 +2872,7 @@
       </c>
       <c r="L32" s="8"/>
     </row>
-    <row r="33" spans="1:12" ht="39.6">
+    <row r="33" spans="1:12" ht="39.6" hidden="1">
       <c r="A33" s="4">
         <v>1</v>
       </c>
@@ -2893,7 +2909,7 @@
       </c>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="1:12" ht="26.4">
+    <row r="34" spans="1:12" ht="26.4" hidden="1">
       <c r="A34" s="4">
         <v>1</v>
       </c>
@@ -2930,7 +2946,7 @@
       </c>
       <c r="L34" s="8"/>
     </row>
-    <row r="35" spans="1:12" ht="26.4">
+    <row r="35" spans="1:12" ht="26.4" hidden="1">
       <c r="A35" s="4">
         <v>1</v>
       </c>
@@ -2967,7 +2983,7 @@
       </c>
       <c r="L35" s="8"/>
     </row>
-    <row r="36" spans="1:12" ht="26.4">
+    <row r="36" spans="1:12" ht="26.4" hidden="1">
       <c r="A36" s="4">
         <v>1</v>
       </c>
@@ -3004,7 +3020,7 @@
       </c>
       <c r="L36" s="8"/>
     </row>
-    <row r="37" spans="1:12" ht="26.4">
+    <row r="37" spans="1:12" ht="26.4" hidden="1">
       <c r="A37" s="4">
         <v>1</v>
       </c>
@@ -3041,7 +3057,7 @@
       </c>
       <c r="L37" s="8"/>
     </row>
-    <row r="38" spans="1:12" ht="26.4">
+    <row r="38" spans="1:12" ht="26.4" hidden="1">
       <c r="A38" s="4">
         <v>1</v>
       </c>
@@ -3078,7 +3094,7 @@
       </c>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" ht="26.4">
+    <row r="39" spans="1:12" ht="26.4" hidden="1">
       <c r="A39" s="4">
         <v>1</v>
       </c>
@@ -3115,7 +3131,7 @@
       </c>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" ht="26.4">
+    <row r="40" spans="1:12" ht="26.4" hidden="1">
       <c r="A40" s="4">
         <v>1</v>
       </c>
@@ -3152,7 +3168,7 @@
       </c>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" ht="26.4">
+    <row r="41" spans="1:12" ht="26.4" hidden="1">
       <c r="A41" s="4">
         <v>1</v>
       </c>
@@ -3189,7 +3205,7 @@
       </c>
       <c r="L41" s="8"/>
     </row>
-    <row r="42" spans="1:12" ht="26.4">
+    <row r="42" spans="1:12" ht="26.4" hidden="1">
       <c r="A42" s="4">
         <v>1</v>
       </c>
@@ -3226,7 +3242,7 @@
       </c>
       <c r="L42" s="8"/>
     </row>
-    <row r="43" spans="1:12" ht="39.6">
+    <row r="43" spans="1:12" ht="39.6" hidden="1">
       <c r="A43" s="4">
         <v>1</v>
       </c>
@@ -3300,7 +3316,7 @@
       </c>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" ht="39.6">
+    <row r="45" spans="1:12" ht="39.6" hidden="1">
       <c r="A45" s="4">
         <v>1</v>
       </c>
@@ -3337,7 +3353,7 @@
       </c>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" ht="39.6">
+    <row r="46" spans="1:12" ht="39.6" hidden="1">
       <c r="A46" s="4">
         <v>1</v>
       </c>
@@ -3448,7 +3464,7 @@
       </c>
       <c r="L48" s="8"/>
     </row>
-    <row r="49" spans="1:12" ht="39.6">
+    <row r="49" spans="1:12" ht="39.6" hidden="1">
       <c r="A49" s="4">
         <v>1</v>
       </c>
@@ -3485,7 +3501,7 @@
       </c>
       <c r="L49" s="8"/>
     </row>
-    <row r="50" spans="1:12" ht="39.6">
+    <row r="50" spans="1:12" ht="39.6" hidden="1">
       <c r="A50" s="4">
         <v>1</v>
       </c>
@@ -3522,7 +3538,7 @@
       </c>
       <c r="L50" s="8"/>
     </row>
-    <row r="51" spans="1:12" ht="39.6">
+    <row r="51" spans="1:12" ht="39.6" hidden="1">
       <c r="A51" s="4">
         <v>1</v>
       </c>
@@ -3559,7 +3575,7 @@
       </c>
       <c r="L51" s="8"/>
     </row>
-    <row r="52" spans="1:12" ht="36" customHeight="1">
+    <row r="52" spans="1:12" ht="36" hidden="1" customHeight="1">
       <c r="A52" s="4">
         <v>1</v>
       </c>
@@ -3594,7 +3610,7 @@
       </c>
       <c r="L52" s="8"/>
     </row>
-    <row r="53" spans="1:12" ht="26.4">
+    <row r="53" spans="1:12" ht="26.4" hidden="1">
       <c r="A53" s="4">
         <v>1</v>
       </c>
@@ -3631,7 +3647,7 @@
       </c>
       <c r="L53" s="8"/>
     </row>
-    <row r="54" spans="1:12" ht="26.4">
+    <row r="54" spans="1:12" ht="26.4" hidden="1">
       <c r="A54" s="4">
         <v>1</v>
       </c>
@@ -3668,7 +3684,7 @@
       </c>
       <c r="L54" s="8"/>
     </row>
-    <row r="55" spans="1:12" ht="26.4">
+    <row r="55" spans="1:12" ht="26.4" hidden="1">
       <c r="A55" s="4">
         <v>1</v>
       </c>
@@ -3705,7 +3721,7 @@
       </c>
       <c r="L55" s="8"/>
     </row>
-    <row r="56" spans="1:12" ht="39.6">
+    <row r="56" spans="1:12" ht="39.6" hidden="1">
       <c r="A56" s="4">
         <v>1</v>
       </c>
@@ -3742,7 +3758,7 @@
       </c>
       <c r="L56" s="8"/>
     </row>
-    <row r="57" spans="1:12" ht="39.6">
+    <row r="57" spans="1:12" ht="39.6" hidden="1">
       <c r="A57" s="4">
         <v>1</v>
       </c>
@@ -3779,7 +3795,7 @@
       </c>
       <c r="L57" s="8"/>
     </row>
-    <row r="58" spans="1:12" ht="39.6">
+    <row r="58" spans="1:12" ht="39.6" hidden="1">
       <c r="A58" s="4">
         <v>1</v>
       </c>
@@ -3816,7 +3832,7 @@
       </c>
       <c r="L58" s="8"/>
     </row>
-    <row r="59" spans="1:12" ht="26.4">
+    <row r="59" spans="1:12" ht="26.4" hidden="1">
       <c r="A59" s="4">
         <v>1</v>
       </c>
@@ -3853,7 +3869,7 @@
       </c>
       <c r="L59" s="8"/>
     </row>
-    <row r="60" spans="1:12" ht="39.6">
+    <row r="60" spans="1:12" ht="39.6" hidden="1">
       <c r="A60" s="4">
         <v>1</v>
       </c>
@@ -3890,7 +3906,7 @@
       </c>
       <c r="L60" s="8"/>
     </row>
-    <row r="61" spans="1:12" ht="39.6">
+    <row r="61" spans="1:12" ht="39.6" hidden="1">
       <c r="A61" s="4">
         <v>1</v>
       </c>
@@ -3927,7 +3943,7 @@
       </c>
       <c r="L61" s="8"/>
     </row>
-    <row r="62" spans="1:12" ht="26.4">
+    <row r="62" spans="1:12" ht="26.4" hidden="1">
       <c r="A62" s="4">
         <v>1</v>
       </c>
@@ -3964,7 +3980,7 @@
       </c>
       <c r="L62" s="8"/>
     </row>
-    <row r="63" spans="1:12" ht="39.6">
+    <row r="63" spans="1:12" ht="39.6" hidden="1">
       <c r="A63" s="4">
         <v>1</v>
       </c>
@@ -4001,7 +4017,7 @@
       </c>
       <c r="L63" s="8"/>
     </row>
-    <row r="64" spans="1:12" ht="26.4">
+    <row r="64" spans="1:12" ht="26.4" hidden="1">
       <c r="A64" s="4">
         <v>1</v>
       </c>
@@ -4038,7 +4054,7 @@
       </c>
       <c r="L64" s="8"/>
     </row>
-    <row r="65" spans="1:12" ht="26.4">
+    <row r="65" spans="1:12" ht="26.4" hidden="1">
       <c r="A65" s="4">
         <v>1</v>
       </c>
@@ -4075,7 +4091,7 @@
       </c>
       <c r="L65" s="8"/>
     </row>
-    <row r="66" spans="1:12" ht="39.6">
+    <row r="66" spans="1:12" ht="39.6" hidden="1">
       <c r="A66" s="4">
         <v>1</v>
       </c>
@@ -4112,7 +4128,7 @@
       </c>
       <c r="L66" s="8"/>
     </row>
-    <row r="67" spans="1:12" ht="32.4" customHeight="1">
+    <row r="67" spans="1:12" ht="32.4" hidden="1" customHeight="1">
       <c r="A67" s="4">
         <v>1</v>
       </c>
@@ -4149,7 +4165,7 @@
       </c>
       <c r="L67" s="8"/>
     </row>
-    <row r="68" spans="1:12" ht="31.8" customHeight="1">
+    <row r="68" spans="1:12" ht="31.8" hidden="1" customHeight="1">
       <c r="A68" s="4">
         <v>1</v>
       </c>
@@ -4186,7 +4202,7 @@
       </c>
       <c r="L68" s="8"/>
     </row>
-    <row r="69" spans="1:12" ht="27" customHeight="1">
+    <row r="69" spans="1:12" ht="27" hidden="1" customHeight="1">
       <c r="A69" s="4">
         <v>1</v>
       </c>
@@ -4221,7 +4237,7 @@
       </c>
       <c r="L69" s="8"/>
     </row>
-    <row r="70" spans="1:12" s="51" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="70" spans="1:12" s="51" customFormat="1" ht="34.200000000000003" hidden="1" customHeight="1">
       <c r="A70" s="43">
         <v>1</v>
       </c>
@@ -4258,7 +4274,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="51" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="71" spans="1:12" s="51" customFormat="1" ht="34.200000000000003" hidden="1" customHeight="1">
       <c r="A71" s="43"/>
       <c r="B71" s="44" t="s">
         <v>27</v>
@@ -4293,7 +4309,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="72" spans="1:12" s="51" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="72" spans="1:12" s="51" customFormat="1" ht="34.200000000000003" hidden="1" customHeight="1">
       <c r="A72" s="43"/>
       <c r="B72" s="44" t="s">
         <v>27</v>
@@ -4328,7 +4344,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="51" customFormat="1" ht="28.2" customHeight="1">
+    <row r="73" spans="1:12" s="51" customFormat="1" ht="28.2" hidden="1" customHeight="1">
       <c r="A73" s="43">
         <v>1</v>
       </c>
@@ -4365,7 +4381,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="28.2" customHeight="1">
+    <row r="74" spans="1:12" ht="28.2" hidden="1" customHeight="1">
       <c r="A74" s="4">
         <v>1</v>
       </c>
@@ -4400,7 +4416,7 @@
       </c>
       <c r="L74" s="8"/>
     </row>
-    <row r="75" spans="1:12" ht="24" customHeight="1">
+    <row r="75" spans="1:12" ht="24" hidden="1" customHeight="1">
       <c r="A75" s="4">
         <v>1</v>
       </c>
@@ -4433,26 +4449,26 @@
       </c>
       <c r="L75" s="8"/>
     </row>
-    <row r="76" spans="1:12" ht="31.8" customHeight="1">
+    <row r="76" spans="1:12" ht="31.8" hidden="1" customHeight="1">
       <c r="A76" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B76" s="119"/>
-      <c r="C76" s="120"/>
-      <c r="D76" s="120"/>
-      <c r="E76" s="120"/>
-      <c r="F76" s="120"/>
-      <c r="G76" s="120"/>
-      <c r="H76" s="120"/>
-      <c r="I76" s="120"/>
-      <c r="J76" s="121"/>
+      <c r="B76" s="63"/>
+      <c r="C76" s="82"/>
+      <c r="D76" s="82"/>
+      <c r="E76" s="82"/>
+      <c r="F76" s="82"/>
+      <c r="G76" s="82"/>
+      <c r="H76" s="82"/>
+      <c r="I76" s="82"/>
+      <c r="J76" s="66"/>
       <c r="K76" s="12">
         <f>SUM(K29:K75)</f>
         <v>1357588</v>
       </c>
       <c r="L76" s="8"/>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" hidden="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -4466,7 +4482,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
     </row>
-    <row r="78" spans="1:12" ht="46.2" customHeight="1">
+    <row r="78" spans="1:12" ht="46.2" hidden="1" customHeight="1">
       <c r="A78" s="3" t="s">
         <v>11</v>
       </c>
@@ -4504,7 +4520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="26.4">
+    <row r="79" spans="1:12" ht="26.4" hidden="1">
       <c r="A79" s="4">
         <v>1</v>
       </c>
@@ -4541,7 +4557,7 @@
       </c>
       <c r="L79" s="8"/>
     </row>
-    <row r="80" spans="1:12" ht="26.4">
+    <row r="80" spans="1:12" ht="26.4" hidden="1">
       <c r="A80" s="4">
         <v>2</v>
       </c>
@@ -4578,7 +4594,7 @@
       </c>
       <c r="L80" s="8"/>
     </row>
-    <row r="81" spans="1:12" ht="26.4">
+    <row r="81" spans="1:12" ht="26.4" hidden="1">
       <c r="A81" s="4">
         <v>3</v>
       </c>
@@ -4615,7 +4631,7 @@
       </c>
       <c r="L81" s="8"/>
     </row>
-    <row r="82" spans="1:12" ht="26.4">
+    <row r="82" spans="1:12" ht="26.4" hidden="1">
       <c r="A82" s="4">
         <v>4</v>
       </c>
@@ -4652,7 +4668,7 @@
       </c>
       <c r="L82" s="8"/>
     </row>
-    <row r="83" spans="1:12" ht="26.4">
+    <row r="83" spans="1:12" ht="26.4" hidden="1">
       <c r="A83" s="4">
         <v>5</v>
       </c>
@@ -4689,7 +4705,7 @@
       </c>
       <c r="L83" s="8"/>
     </row>
-    <row r="84" spans="1:12" ht="26.4">
+    <row r="84" spans="1:12" ht="26.4" hidden="1">
       <c r="A84" s="4">
         <v>6</v>
       </c>
@@ -4726,7 +4742,7 @@
       </c>
       <c r="L84" s="8"/>
     </row>
-    <row r="85" spans="1:12" ht="26.4">
+    <row r="85" spans="1:12" ht="26.4" hidden="1">
       <c r="A85" s="4">
         <v>7</v>
       </c>
@@ -4763,7 +4779,7 @@
       </c>
       <c r="L85" s="8"/>
     </row>
-    <row r="86" spans="1:12" ht="26.4">
+    <row r="86" spans="1:12" ht="26.4" hidden="1">
       <c r="A86" s="4">
         <v>8</v>
       </c>
@@ -4800,7 +4816,7 @@
       </c>
       <c r="L86" s="8"/>
     </row>
-    <row r="87" spans="1:12" ht="26.4">
+    <row r="87" spans="1:12" ht="26.4" hidden="1">
       <c r="A87" s="4">
         <v>9</v>
       </c>
@@ -4837,7 +4853,7 @@
       </c>
       <c r="L87" s="8"/>
     </row>
-    <row r="88" spans="1:12" ht="26.4">
+    <row r="88" spans="1:12" ht="26.4" hidden="1">
       <c r="A88" s="4">
         <v>10</v>
       </c>
@@ -4874,7 +4890,7 @@
       </c>
       <c r="L88" s="8"/>
     </row>
-    <row r="89" spans="1:12" ht="26.4">
+    <row r="89" spans="1:12" ht="26.4" hidden="1">
       <c r="A89" s="4">
         <v>11</v>
       </c>
@@ -4911,7 +4927,7 @@
       </c>
       <c r="L89" s="8"/>
     </row>
-    <row r="90" spans="1:12" ht="26.4">
+    <row r="90" spans="1:12" ht="26.4" hidden="1">
       <c r="A90" s="4">
         <v>12</v>
       </c>
@@ -4948,7 +4964,7 @@
       </c>
       <c r="L90" s="8"/>
     </row>
-    <row r="91" spans="1:12" ht="26.4">
+    <row r="91" spans="1:12" ht="26.4" hidden="1">
       <c r="A91" s="4">
         <v>13</v>
       </c>
@@ -4985,7 +5001,7 @@
       </c>
       <c r="L91" s="8"/>
     </row>
-    <row r="92" spans="1:12" ht="26.4">
+    <row r="92" spans="1:12" ht="26.4" hidden="1">
       <c r="A92" s="4">
         <v>14</v>
       </c>
@@ -5022,7 +5038,7 @@
       </c>
       <c r="L92" s="8"/>
     </row>
-    <row r="93" spans="1:12" ht="26.4">
+    <row r="93" spans="1:12" ht="26.4" hidden="1">
       <c r="A93" s="4">
         <v>15</v>
       </c>
@@ -5059,7 +5075,7 @@
       </c>
       <c r="L93" s="8"/>
     </row>
-    <row r="94" spans="1:12" ht="26.4">
+    <row r="94" spans="1:12" ht="26.4" hidden="1">
       <c r="A94" s="4">
         <v>16</v>
       </c>
@@ -5096,7 +5112,7 @@
       </c>
       <c r="L94" s="8"/>
     </row>
-    <row r="95" spans="1:12" ht="39.6">
+    <row r="95" spans="1:12" ht="39.6" hidden="1">
       <c r="A95" s="4">
         <v>17</v>
       </c>
@@ -5133,7 +5149,7 @@
       </c>
       <c r="L95" s="8"/>
     </row>
-    <row r="96" spans="1:12" ht="26.4">
+    <row r="96" spans="1:12" ht="26.4" hidden="1">
       <c r="A96" s="4">
         <v>18</v>
       </c>
@@ -5170,7 +5186,7 @@
       </c>
       <c r="L96" s="8"/>
     </row>
-    <row r="97" spans="1:12" ht="26.4">
+    <row r="97" spans="1:12" ht="26.4" hidden="1">
       <c r="A97" s="4">
         <v>19</v>
       </c>
@@ -5207,7 +5223,7 @@
       </c>
       <c r="L97" s="8"/>
     </row>
-    <row r="98" spans="1:12" ht="26.4">
+    <row r="98" spans="1:12" ht="26.4" hidden="1">
       <c r="A98" s="4">
         <v>20</v>
       </c>
@@ -5244,7 +5260,7 @@
       </c>
       <c r="L98" s="8"/>
     </row>
-    <row r="99" spans="1:12" ht="26.4">
+    <row r="99" spans="1:12" ht="26.4" hidden="1">
       <c r="A99" s="4">
         <v>21</v>
       </c>
@@ -5281,7 +5297,7 @@
       </c>
       <c r="L99" s="8"/>
     </row>
-    <row r="100" spans="1:12" ht="39.6">
+    <row r="100" spans="1:12" ht="39.6" hidden="1">
       <c r="A100" s="4">
         <v>22</v>
       </c>
@@ -5318,7 +5334,7 @@
       </c>
       <c r="L100" s="8"/>
     </row>
-    <row r="101" spans="1:12" ht="39.6">
+    <row r="101" spans="1:12" ht="39.6" hidden="1">
       <c r="A101" s="4">
         <v>23</v>
       </c>
@@ -5355,7 +5371,7 @@
       </c>
       <c r="L101" s="8"/>
     </row>
-    <row r="102" spans="1:12" ht="39.6">
+    <row r="102" spans="1:12" ht="39.6" hidden="1">
       <c r="A102" s="4">
         <v>24</v>
       </c>
@@ -5392,7 +5408,7 @@
       </c>
       <c r="L102" s="8"/>
     </row>
-    <row r="103" spans="1:12" ht="39.6">
+    <row r="103" spans="1:12" ht="39.6" hidden="1">
       <c r="A103" s="4">
         <v>25</v>
       </c>
@@ -5429,7 +5445,7 @@
       </c>
       <c r="L103" s="8"/>
     </row>
-    <row r="104" spans="1:12" ht="39.6">
+    <row r="104" spans="1:12" ht="39.6" hidden="1">
       <c r="A104" s="4">
         <v>26</v>
       </c>
@@ -5466,7 +5482,7 @@
       </c>
       <c r="L104" s="8"/>
     </row>
-    <row r="105" spans="1:12" ht="39.6">
+    <row r="105" spans="1:12" ht="39.6" hidden="1">
       <c r="A105" s="4">
         <v>27</v>
       </c>
@@ -5503,7 +5519,7 @@
       </c>
       <c r="L105" s="8"/>
     </row>
-    <row r="106" spans="1:12" ht="39.6">
+    <row r="106" spans="1:12" ht="39.6" hidden="1">
       <c r="A106" s="4">
         <v>28</v>
       </c>
@@ -5540,7 +5556,7 @@
       </c>
       <c r="L106" s="8"/>
     </row>
-    <row r="107" spans="1:12" ht="39.6">
+    <row r="107" spans="1:12" ht="39.6" hidden="1">
       <c r="A107" s="4">
         <v>29</v>
       </c>
@@ -5577,7 +5593,7 @@
       </c>
       <c r="L107" s="8"/>
     </row>
-    <row r="108" spans="1:12" ht="39.6">
+    <row r="108" spans="1:12" ht="39.6" hidden="1">
       <c r="A108" s="4">
         <v>30</v>
       </c>
@@ -5614,7 +5630,7 @@
       </c>
       <c r="L108" s="8"/>
     </row>
-    <row r="109" spans="1:12" ht="39.6">
+    <row r="109" spans="1:12" ht="39.6" hidden="1">
       <c r="A109" s="4">
         <v>31</v>
       </c>
@@ -5651,7 +5667,7 @@
       </c>
       <c r="L109" s="8"/>
     </row>
-    <row r="110" spans="1:12" ht="39.6">
+    <row r="110" spans="1:12" ht="39.6" hidden="1">
       <c r="A110" s="4">
         <v>32</v>
       </c>
@@ -5688,7 +5704,7 @@
       </c>
       <c r="L110" s="8"/>
     </row>
-    <row r="111" spans="1:12" ht="39.6">
+    <row r="111" spans="1:12" ht="39.6" hidden="1">
       <c r="A111" s="4">
         <v>33</v>
       </c>
@@ -5725,7 +5741,7 @@
       </c>
       <c r="L111" s="8"/>
     </row>
-    <row r="112" spans="1:12" ht="39.6">
+    <row r="112" spans="1:12" ht="39.6" hidden="1">
       <c r="A112" s="4">
         <v>34</v>
       </c>
@@ -5762,7 +5778,7 @@
       </c>
       <c r="L112" s="8"/>
     </row>
-    <row r="113" spans="1:12" ht="39.6">
+    <row r="113" spans="1:12" ht="39.6" hidden="1">
       <c r="A113" s="4">
         <v>35</v>
       </c>
@@ -5799,7 +5815,7 @@
       </c>
       <c r="L113" s="8"/>
     </row>
-    <row r="114" spans="1:12" ht="39.6">
+    <row r="114" spans="1:12" ht="39.6" hidden="1">
       <c r="A114" s="4">
         <v>36</v>
       </c>
@@ -5836,7 +5852,7 @@
       </c>
       <c r="L114" s="8"/>
     </row>
-    <row r="115" spans="1:12" ht="39.6">
+    <row r="115" spans="1:12" ht="39.6" hidden="1">
       <c r="A115" s="4">
         <v>37</v>
       </c>
@@ -5873,7 +5889,7 @@
       </c>
       <c r="L115" s="8"/>
     </row>
-    <row r="116" spans="1:12" ht="39.6">
+    <row r="116" spans="1:12" ht="39.6" hidden="1">
       <c r="A116" s="4">
         <v>38</v>
       </c>
@@ -5910,7 +5926,7 @@
       </c>
       <c r="L116" s="8"/>
     </row>
-    <row r="117" spans="1:12" ht="39.6">
+    <row r="117" spans="1:12" ht="39.6" hidden="1">
       <c r="A117" s="4">
         <v>39</v>
       </c>
@@ -5947,7 +5963,7 @@
       </c>
       <c r="L117" s="8"/>
     </row>
-    <row r="118" spans="1:12" ht="39.6">
+    <row r="118" spans="1:12" ht="39.6" hidden="1">
       <c r="A118" s="4">
         <v>40</v>
       </c>
@@ -5984,7 +6000,7 @@
       </c>
       <c r="L118" s="8"/>
     </row>
-    <row r="119" spans="1:12" ht="39.6">
+    <row r="119" spans="1:12" ht="39.6" hidden="1">
       <c r="A119" s="4">
         <v>41</v>
       </c>
@@ -6021,7 +6037,7 @@
       </c>
       <c r="L119" s="8"/>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" hidden="1">
       <c r="A120" s="4">
         <v>42</v>
       </c>
@@ -6058,7 +6074,7 @@
       </c>
       <c r="L120" s="8"/>
     </row>
-    <row r="121" spans="1:12" ht="26.4">
+    <row r="121" spans="1:12" ht="26.4" hidden="1">
       <c r="A121" s="4">
         <v>43</v>
       </c>
@@ -6095,7 +6111,7 @@
       </c>
       <c r="L121" s="8"/>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" hidden="1">
       <c r="A122" s="4">
         <v>44</v>
       </c>
@@ -6132,7 +6148,7 @@
       </c>
       <c r="L122" s="8"/>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" hidden="1">
       <c r="A123" s="4">
         <v>45</v>
       </c>
@@ -6169,7 +6185,7 @@
       </c>
       <c r="L123" s="8"/>
     </row>
-    <row r="124" spans="1:12" ht="14.4" customHeight="1">
+    <row r="124" spans="1:12" ht="14.4" hidden="1" customHeight="1">
       <c r="A124" s="4">
         <v>46</v>
       </c>
@@ -6206,7 +6222,7 @@
       </c>
       <c r="L124" s="8"/>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" hidden="1">
       <c r="A125" s="4">
         <v>47</v>
       </c>
@@ -6243,7 +6259,7 @@
       </c>
       <c r="L125" s="8"/>
     </row>
-    <row r="126" spans="1:12" ht="26.4">
+    <row r="126" spans="1:12" ht="26.4" hidden="1">
       <c r="A126" s="4">
         <v>48</v>
       </c>
@@ -6280,7 +6296,7 @@
       </c>
       <c r="L126" s="8"/>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:12" hidden="1">
       <c r="A127" s="4">
         <v>49</v>
       </c>
@@ -6317,7 +6333,7 @@
       </c>
       <c r="L127" s="8"/>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" hidden="1">
       <c r="A128" s="4">
         <v>50</v>
       </c>
@@ -6354,7 +6370,7 @@
       </c>
       <c r="L128" s="8"/>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" hidden="1">
       <c r="A129" s="4">
         <v>51</v>
       </c>
@@ -6391,7 +6407,7 @@
       </c>
       <c r="L129" s="8"/>
     </row>
-    <row r="130" spans="1:12" ht="26.4">
+    <row r="130" spans="1:12" ht="26.4" hidden="1">
       <c r="A130" s="4">
         <v>52</v>
       </c>
@@ -6428,7 +6444,7 @@
       </c>
       <c r="L130" s="8"/>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" hidden="1">
       <c r="A131" s="4">
         <v>53</v>
       </c>
@@ -6465,7 +6481,7 @@
       </c>
       <c r="L131" s="8"/>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132" spans="1:12" hidden="1">
       <c r="A132" s="4">
         <v>54</v>
       </c>
@@ -6502,7 +6518,7 @@
       </c>
       <c r="L132" s="8"/>
     </row>
-    <row r="133" spans="1:12" ht="39.6">
+    <row r="133" spans="1:12" ht="39.6" hidden="1">
       <c r="A133" s="4">
         <v>55</v>
       </c>
@@ -6539,7 +6555,7 @@
       </c>
       <c r="L133" s="8"/>
     </row>
-    <row r="134" spans="1:12" ht="26.4">
+    <row r="134" spans="1:12" ht="26.4" hidden="1">
       <c r="A134" s="4">
         <v>56</v>
       </c>
@@ -6576,7 +6592,7 @@
       </c>
       <c r="L134" s="8"/>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135" spans="1:12" hidden="1">
       <c r="A135" s="4">
         <v>57</v>
       </c>
@@ -6613,7 +6629,7 @@
       </c>
       <c r="L135" s="8"/>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136" spans="1:12" hidden="1">
       <c r="A136" s="4">
         <v>58</v>
       </c>
@@ -6650,7 +6666,7 @@
       </c>
       <c r="L136" s="8"/>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" hidden="1">
       <c r="A137" s="4">
         <v>59</v>
       </c>
@@ -6687,7 +6703,7 @@
       </c>
       <c r="L137" s="8"/>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" hidden="1">
       <c r="A138" s="4">
         <v>60</v>
       </c>
@@ -6724,7 +6740,7 @@
       </c>
       <c r="L138" s="8"/>
     </row>
-    <row r="139" spans="1:12" ht="26.4">
+    <row r="139" spans="1:12" ht="26.4" hidden="1">
       <c r="A139" s="4">
         <v>61</v>
       </c>
@@ -6761,7 +6777,7 @@
       </c>
       <c r="L139" s="8"/>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" hidden="1">
       <c r="A140" s="4">
         <v>62</v>
       </c>
@@ -6798,7 +6814,7 @@
       </c>
       <c r="L140" s="8"/>
     </row>
-    <row r="141" spans="1:12" ht="26.4">
+    <row r="141" spans="1:12" ht="26.4" hidden="1">
       <c r="A141" s="4">
         <v>63</v>
       </c>
@@ -6835,7 +6851,7 @@
       </c>
       <c r="L141" s="8"/>
     </row>
-    <row r="142" spans="1:12" ht="26.4">
+    <row r="142" spans="1:12" ht="26.4" hidden="1">
       <c r="A142" s="4">
         <v>64</v>
       </c>
@@ -6872,7 +6888,7 @@
       </c>
       <c r="L142" s="8"/>
     </row>
-    <row r="143" spans="1:12" ht="26.4">
+    <row r="143" spans="1:12" ht="26.4" hidden="1">
       <c r="A143" s="4">
         <v>65</v>
       </c>
@@ -6909,7 +6925,7 @@
       </c>
       <c r="L143" s="8"/>
     </row>
-    <row r="144" spans="1:12" ht="39.6">
+    <row r="144" spans="1:12" ht="39.6" hidden="1">
       <c r="A144" s="4">
         <v>66</v>
       </c>
@@ -6946,7 +6962,7 @@
       </c>
       <c r="L144" s="8"/>
     </row>
-    <row r="145" spans="1:12" ht="26.4">
+    <row r="145" spans="1:12" ht="26.4" hidden="1">
       <c r="A145" s="4">
         <v>67</v>
       </c>
@@ -6983,7 +6999,7 @@
       </c>
       <c r="L145" s="8"/>
     </row>
-    <row r="146" spans="1:12" ht="39.6">
+    <row r="146" spans="1:12" ht="39.6" hidden="1">
       <c r="A146" s="4">
         <v>68</v>
       </c>
@@ -7020,7 +7036,7 @@
       </c>
       <c r="L146" s="8"/>
     </row>
-    <row r="147" spans="1:12" ht="26.4">
+    <row r="147" spans="1:12" ht="26.4" hidden="1">
       <c r="A147" s="4">
         <v>69</v>
       </c>
@@ -7057,7 +7073,7 @@
       </c>
       <c r="L147" s="8"/>
     </row>
-    <row r="148" spans="1:12" ht="39.6">
+    <row r="148" spans="1:12" ht="39.6" hidden="1">
       <c r="A148" s="4">
         <v>70</v>
       </c>
@@ -7094,7 +7110,7 @@
       </c>
       <c r="L148" s="8"/>
     </row>
-    <row r="149" spans="1:12" ht="39.6">
+    <row r="149" spans="1:12" ht="39.6" hidden="1">
       <c r="A149" s="4">
         <v>71</v>
       </c>
@@ -7131,7 +7147,7 @@
       </c>
       <c r="L149" s="8"/>
     </row>
-    <row r="150" spans="1:12" ht="39.6">
+    <row r="150" spans="1:12" ht="39.6" hidden="1">
       <c r="A150" s="4">
         <v>72</v>
       </c>
@@ -7168,7 +7184,7 @@
       </c>
       <c r="L150" s="8"/>
     </row>
-    <row r="151" spans="1:12" ht="26.4">
+    <row r="151" spans="1:12" ht="26.4" hidden="1">
       <c r="A151" s="4">
         <v>73</v>
       </c>
@@ -7205,7 +7221,7 @@
       </c>
       <c r="L151" s="8"/>
     </row>
-    <row r="152" spans="1:12" ht="39.6">
+    <row r="152" spans="1:12" ht="39.6" hidden="1">
       <c r="A152" s="4">
         <v>74</v>
       </c>
@@ -7242,7 +7258,7 @@
       </c>
       <c r="L152" s="8"/>
     </row>
-    <row r="153" spans="1:12" ht="26.4">
+    <row r="153" spans="1:12" ht="26.4" hidden="1">
       <c r="A153" s="4">
         <v>75</v>
       </c>
@@ -7279,7 +7295,7 @@
       </c>
       <c r="L153" s="8"/>
     </row>
-    <row r="154" spans="1:12" ht="39.6">
+    <row r="154" spans="1:12" ht="39.6" hidden="1">
       <c r="A154" s="4">
         <v>76</v>
       </c>
@@ -7316,7 +7332,7 @@
       </c>
       <c r="L154" s="8"/>
     </row>
-    <row r="155" spans="1:12" ht="39.6">
+    <row r="155" spans="1:12" ht="39.6" hidden="1">
       <c r="A155" s="4">
         <v>77</v>
       </c>
@@ -7353,7 +7369,7 @@
       </c>
       <c r="L155" s="8"/>
     </row>
-    <row r="156" spans="1:12" ht="26.4">
+    <row r="156" spans="1:12" ht="26.4" hidden="1">
       <c r="A156" s="4">
         <v>78</v>
       </c>
@@ -7390,7 +7406,7 @@
       </c>
       <c r="L156" s="8"/>
     </row>
-    <row r="157" spans="1:12" ht="39.6">
+    <row r="157" spans="1:12" ht="39.6" hidden="1">
       <c r="A157" s="4">
         <v>79</v>
       </c>
@@ -7427,7 +7443,7 @@
       </c>
       <c r="L157" s="8"/>
     </row>
-    <row r="158" spans="1:12" ht="26.4">
+    <row r="158" spans="1:12" ht="26.4" hidden="1">
       <c r="A158" s="4">
         <v>80</v>
       </c>
@@ -7464,7 +7480,7 @@
       </c>
       <c r="L158" s="8"/>
     </row>
-    <row r="159" spans="1:12" ht="39.6">
+    <row r="159" spans="1:12" ht="39.6" hidden="1">
       <c r="A159" s="4">
         <v>81</v>
       </c>
@@ -7501,7 +7517,7 @@
       </c>
       <c r="L159" s="8"/>
     </row>
-    <row r="160" spans="1:12" ht="39.6">
+    <row r="160" spans="1:12" ht="39.6" hidden="1">
       <c r="A160" s="4">
         <v>82</v>
       </c>
@@ -7538,7 +7554,7 @@
       </c>
       <c r="L160" s="8"/>
     </row>
-    <row r="161" spans="1:12" ht="26.4">
+    <row r="161" spans="1:12" ht="26.4" hidden="1">
       <c r="A161" s="4">
         <v>83</v>
       </c>
@@ -7575,7 +7591,7 @@
       </c>
       <c r="L161" s="8"/>
     </row>
-    <row r="162" spans="1:12" ht="15.6">
+    <row r="162" spans="1:12" ht="15.6" hidden="1">
       <c r="A162" s="4">
         <v>84</v>
       </c>
@@ -7612,7 +7628,7 @@
       </c>
       <c r="L162" s="8"/>
     </row>
-    <row r="163" spans="1:12" ht="26.4">
+    <row r="163" spans="1:12" ht="26.4" hidden="1">
       <c r="A163" s="4">
         <v>85</v>
       </c>
@@ -7649,7 +7665,7 @@
       </c>
       <c r="L163" s="8"/>
     </row>
-    <row r="164" spans="1:12" ht="15.6">
+    <row r="164" spans="1:12" ht="15.6" hidden="1">
       <c r="A164" s="4">
         <v>86</v>
       </c>
@@ -7686,7 +7702,7 @@
       </c>
       <c r="L164" s="8"/>
     </row>
-    <row r="165" spans="1:12" ht="15.6">
+    <row r="165" spans="1:12" ht="15.6" hidden="1">
       <c r="A165" s="4">
         <v>87</v>
       </c>
@@ -7723,7 +7739,7 @@
       </c>
       <c r="L165" s="8"/>
     </row>
-    <row r="166" spans="1:12" ht="26.4">
+    <row r="166" spans="1:12" ht="26.4" hidden="1">
       <c r="A166" s="4">
         <v>88</v>
       </c>
@@ -7760,7 +7776,7 @@
       </c>
       <c r="L166" s="8"/>
     </row>
-    <row r="167" spans="1:12" ht="26.4">
+    <row r="167" spans="1:12" ht="26.4" hidden="1">
       <c r="A167" s="4">
         <v>89</v>
       </c>
@@ -7797,7 +7813,7 @@
       </c>
       <c r="L167" s="8"/>
     </row>
-    <row r="168" spans="1:12" ht="15.6">
+    <row r="168" spans="1:12" ht="15.6" hidden="1">
       <c r="A168" s="4">
         <v>90</v>
       </c>
@@ -7834,7 +7850,7 @@
       </c>
       <c r="L168" s="8"/>
     </row>
-    <row r="169" spans="1:12" ht="52.8">
+    <row r="169" spans="1:12" ht="52.8" hidden="1">
       <c r="A169" s="4">
         <v>91</v>
       </c>
@@ -7871,7 +7887,7 @@
       </c>
       <c r="L169" s="8"/>
     </row>
-    <row r="170" spans="1:12" ht="30.6" customHeight="1">
+    <row r="170" spans="1:12" ht="30.6" hidden="1" customHeight="1">
       <c r="A170" s="4">
         <v>92</v>
       </c>
@@ -7906,7 +7922,7 @@
       </c>
       <c r="L170" s="8"/>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:12" hidden="1">
       <c r="A171" s="4">
         <v>93</v>
       </c>
@@ -7943,26 +7959,26 @@
       </c>
       <c r="L171" s="8"/>
     </row>
-    <row r="172" spans="1:12" ht="30.45" customHeight="1">
+    <row r="172" spans="1:12" ht="30.45" hidden="1" customHeight="1">
       <c r="A172" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B172" s="119"/>
-      <c r="C172" s="120"/>
-      <c r="D172" s="120"/>
-      <c r="E172" s="120"/>
-      <c r="F172" s="120"/>
-      <c r="G172" s="120"/>
-      <c r="H172" s="120"/>
-      <c r="I172" s="120"/>
-      <c r="J172" s="121"/>
+      <c r="B172" s="63"/>
+      <c r="C172" s="82"/>
+      <c r="D172" s="82"/>
+      <c r="E172" s="82"/>
+      <c r="F172" s="82"/>
+      <c r="G172" s="82"/>
+      <c r="H172" s="82"/>
+      <c r="I172" s="82"/>
+      <c r="J172" s="66"/>
       <c r="K172" s="12">
         <f>SUM(K79:K171)</f>
         <v>1612288.5</v>
       </c>
       <c r="L172" s="14"/>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" hidden="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -7976,7 +7992,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
     </row>
-    <row r="174" spans="1:12" ht="26.4">
+    <row r="174" spans="1:12" ht="26.4" hidden="1">
       <c r="A174" s="3" t="s">
         <v>11</v>
       </c>
@@ -8014,7 +8030,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="26.4">
+    <row r="175" spans="1:12" ht="26.4" hidden="1">
       <c r="A175" s="4">
         <v>1</v>
       </c>
@@ -8051,7 +8067,7 @@
       </c>
       <c r="L175" s="8"/>
     </row>
-    <row r="176" spans="1:12" ht="26.4">
+    <row r="176" spans="1:12" ht="26.4" hidden="1">
       <c r="A176" s="4">
         <v>2</v>
       </c>
@@ -8088,7 +8104,7 @@
       </c>
       <c r="L176" s="8"/>
     </row>
-    <row r="177" spans="1:12" ht="26.4">
+    <row r="177" spans="1:12" ht="26.4" hidden="1">
       <c r="A177" s="4">
         <v>3</v>
       </c>
@@ -8125,7 +8141,7 @@
       </c>
       <c r="L177" s="8"/>
     </row>
-    <row r="178" spans="1:12" ht="26.4">
+    <row r="178" spans="1:12" ht="26.4" hidden="1">
       <c r="A178" s="4">
         <v>4</v>
       </c>
@@ -8162,7 +8178,7 @@
       </c>
       <c r="L178" s="8"/>
     </row>
-    <row r="179" spans="1:12" ht="26.4">
+    <row r="179" spans="1:12" ht="26.4" hidden="1">
       <c r="A179" s="4">
         <v>5</v>
       </c>
@@ -8199,7 +8215,7 @@
       </c>
       <c r="L179" s="8"/>
     </row>
-    <row r="180" spans="1:12" ht="26.4">
+    <row r="180" spans="1:12" ht="26.4" hidden="1">
       <c r="A180" s="4">
         <v>6</v>
       </c>
@@ -8236,7 +8252,7 @@
       </c>
       <c r="L180" s="8"/>
     </row>
-    <row r="181" spans="1:12" ht="26.4">
+    <row r="181" spans="1:12" ht="26.4" hidden="1">
       <c r="A181" s="4">
         <v>7</v>
       </c>
@@ -8273,7 +8289,7 @@
       </c>
       <c r="L181" s="8"/>
     </row>
-    <row r="182" spans="1:12" ht="26.4">
+    <row r="182" spans="1:12" ht="26.4" hidden="1">
       <c r="A182" s="4">
         <v>8</v>
       </c>
@@ -8310,7 +8326,7 @@
       </c>
       <c r="L182" s="8"/>
     </row>
-    <row r="183" spans="1:12" ht="26.4">
+    <row r="183" spans="1:12" ht="26.4" hidden="1">
       <c r="A183" s="4">
         <v>9</v>
       </c>
@@ -8347,7 +8363,7 @@
       </c>
       <c r="L183" s="8"/>
     </row>
-    <row r="184" spans="1:12" ht="26.4">
+    <row r="184" spans="1:12" ht="26.4" hidden="1">
       <c r="A184" s="4">
         <v>10</v>
       </c>
@@ -8384,7 +8400,7 @@
       </c>
       <c r="L184" s="8"/>
     </row>
-    <row r="185" spans="1:12" ht="26.4">
+    <row r="185" spans="1:12" ht="26.4" hidden="1">
       <c r="A185" s="4">
         <v>11</v>
       </c>
@@ -8421,7 +8437,7 @@
       </c>
       <c r="L185" s="8"/>
     </row>
-    <row r="186" spans="1:12" ht="26.4">
+    <row r="186" spans="1:12" ht="26.4" hidden="1">
       <c r="A186" s="4">
         <v>12</v>
       </c>
@@ -8458,7 +8474,7 @@
       </c>
       <c r="L186" s="8"/>
     </row>
-    <row r="187" spans="1:12" ht="26.4">
+    <row r="187" spans="1:12" ht="26.4" hidden="1">
       <c r="A187" s="4">
         <v>13</v>
       </c>
@@ -8495,7 +8511,7 @@
       </c>
       <c r="L187" s="8"/>
     </row>
-    <row r="188" spans="1:12" ht="39.6">
+    <row r="188" spans="1:12" ht="39.6" hidden="1" customHeight="1">
       <c r="A188" s="4">
         <v>14</v>
       </c>
@@ -8532,7 +8548,7 @@
       </c>
       <c r="L188" s="8"/>
     </row>
-    <row r="189" spans="1:12" ht="52.8">
+    <row r="189" spans="1:12" ht="52.8" hidden="1">
       <c r="A189" s="4">
         <v>15</v>
       </c>
@@ -8569,7 +8585,7 @@
       </c>
       <c r="L189" s="8"/>
     </row>
-    <row r="190" spans="1:12" ht="26.4">
+    <row r="190" spans="1:12" ht="26.4" hidden="1">
       <c r="A190" s="4">
         <v>16</v>
       </c>
@@ -8606,7 +8622,7 @@
       </c>
       <c r="L190" s="8"/>
     </row>
-    <row r="191" spans="1:12" ht="26.4">
+    <row r="191" spans="1:12" ht="26.4" hidden="1">
       <c r="A191" s="4">
         <v>17</v>
       </c>
@@ -8643,7 +8659,7 @@
       </c>
       <c r="L191" s="8"/>
     </row>
-    <row r="192" spans="1:12" ht="26.4">
+    <row r="192" spans="1:12" ht="26.4" hidden="1">
       <c r="A192" s="4">
         <v>18</v>
       </c>
@@ -8680,7 +8696,7 @@
       </c>
       <c r="L192" s="8"/>
     </row>
-    <row r="193" spans="1:12" ht="26.4">
+    <row r="193" spans="1:12" ht="26.4" hidden="1">
       <c r="A193" s="4">
         <v>19</v>
       </c>
@@ -8717,7 +8733,7 @@
       </c>
       <c r="L193" s="8"/>
     </row>
-    <row r="194" spans="1:12" ht="26.4">
+    <row r="194" spans="1:12" ht="26.4" hidden="1">
       <c r="A194" s="4">
         <v>20</v>
       </c>
@@ -8754,7 +8770,7 @@
       </c>
       <c r="L194" s="8"/>
     </row>
-    <row r="195" spans="1:12" ht="39.6">
+    <row r="195" spans="1:12" ht="39.6" hidden="1">
       <c r="A195" s="4">
         <v>21</v>
       </c>
@@ -8791,7 +8807,7 @@
       </c>
       <c r="L195" s="8"/>
     </row>
-    <row r="196" spans="1:12" ht="15.6">
+    <row r="196" spans="1:12" ht="15.6" hidden="1">
       <c r="A196" s="4">
         <v>22</v>
       </c>
@@ -8814,7 +8830,7 @@
       </c>
       <c r="L196" s="8"/>
     </row>
-    <row r="197" spans="1:12" ht="26.4">
+    <row r="197" spans="1:12" ht="26.4" hidden="1">
       <c r="A197" s="4">
         <v>23</v>
       </c>
@@ -8851,7 +8867,7 @@
       </c>
       <c r="L197" s="8"/>
     </row>
-    <row r="198" spans="1:12" ht="26.4">
+    <row r="198" spans="1:12" ht="26.4" hidden="1">
       <c r="A198" s="4">
         <v>24</v>
       </c>
@@ -8888,7 +8904,7 @@
       </c>
       <c r="L198" s="8"/>
     </row>
-    <row r="199" spans="1:12" ht="26.4">
+    <row r="199" spans="1:12" ht="26.4" hidden="1">
       <c r="A199" s="4">
         <v>25</v>
       </c>
@@ -8925,7 +8941,7 @@
       </c>
       <c r="L199" s="8"/>
     </row>
-    <row r="200" spans="1:12" ht="39.6">
+    <row r="200" spans="1:12" ht="39.6" hidden="1">
       <c r="A200" s="4">
         <v>26</v>
       </c>
@@ -8962,7 +8978,7 @@
       </c>
       <c r="L200" s="8"/>
     </row>
-    <row r="201" spans="1:12" ht="26.4">
+    <row r="201" spans="1:12" ht="26.4" hidden="1">
       <c r="A201" s="4">
         <v>27</v>
       </c>
@@ -8999,7 +9015,7 @@
       </c>
       <c r="L201" s="8"/>
     </row>
-    <row r="202" spans="1:12" ht="26.4">
+    <row r="202" spans="1:12" ht="26.4" hidden="1">
       <c r="A202" s="4">
         <v>28</v>
       </c>
@@ -9036,7 +9052,7 @@
       </c>
       <c r="L202" s="8"/>
     </row>
-    <row r="203" spans="1:12" ht="26.4">
+    <row r="203" spans="1:12" ht="26.4" hidden="1">
       <c r="A203" s="4">
         <v>29</v>
       </c>
@@ -9073,7 +9089,7 @@
       </c>
       <c r="L203" s="8"/>
     </row>
-    <row r="204" spans="1:12" ht="26.4">
+    <row r="204" spans="1:12" ht="26.4" hidden="1">
       <c r="A204" s="4">
         <v>30</v>
       </c>
@@ -9110,7 +9126,7 @@
       </c>
       <c r="L204" s="8"/>
     </row>
-    <row r="205" spans="1:12" ht="26.4">
+    <row r="205" spans="1:12" ht="26.4" hidden="1">
       <c r="A205" s="4">
         <v>31</v>
       </c>
@@ -9147,7 +9163,7 @@
       </c>
       <c r="L205" s="8"/>
     </row>
-    <row r="206" spans="1:12" ht="26.4">
+    <row r="206" spans="1:12" ht="26.4" hidden="1">
       <c r="A206" s="4">
         <v>32</v>
       </c>
@@ -9184,7 +9200,7 @@
       </c>
       <c r="L206" s="8"/>
     </row>
-    <row r="207" spans="1:12" ht="26.4">
+    <row r="207" spans="1:12" ht="26.4" hidden="1">
       <c r="A207" s="4">
         <v>33</v>
       </c>
@@ -9221,7 +9237,7 @@
       </c>
       <c r="L207" s="8"/>
     </row>
-    <row r="208" spans="1:12" ht="26.4">
+    <row r="208" spans="1:12" ht="26.4" hidden="1">
       <c r="A208" s="4">
         <v>34</v>
       </c>
@@ -9258,7 +9274,7 @@
       </c>
       <c r="L208" s="8"/>
     </row>
-    <row r="209" spans="1:12" ht="26.4">
+    <row r="209" spans="1:12" ht="26.4" hidden="1">
       <c r="A209" s="4">
         <v>35</v>
       </c>
@@ -9295,7 +9311,7 @@
       </c>
       <c r="L209" s="8"/>
     </row>
-    <row r="210" spans="1:12" ht="26.4">
+    <row r="210" spans="1:12" ht="26.4" hidden="1">
       <c r="A210" s="4">
         <v>36</v>
       </c>
@@ -9332,7 +9348,7 @@
       </c>
       <c r="L210" s="8"/>
     </row>
-    <row r="211" spans="1:12" ht="26.4">
+    <row r="211" spans="1:12" ht="26.4" hidden="1">
       <c r="A211" s="4">
         <v>37</v>
       </c>
@@ -9369,7 +9385,7 @@
       </c>
       <c r="L211" s="8"/>
     </row>
-    <row r="212" spans="1:12" ht="26.4">
+    <row r="212" spans="1:12" ht="26.4" hidden="1">
       <c r="A212" s="4">
         <v>38</v>
       </c>
@@ -9406,7 +9422,7 @@
       </c>
       <c r="L212" s="8"/>
     </row>
-    <row r="213" spans="1:12" ht="26.4">
+    <row r="213" spans="1:12" ht="26.4" hidden="1">
       <c r="A213" s="4">
         <v>39</v>
       </c>
@@ -9443,7 +9459,7 @@
       </c>
       <c r="L213" s="8"/>
     </row>
-    <row r="214" spans="1:12" ht="26.4">
+    <row r="214" spans="1:12" ht="26.4" hidden="1">
       <c r="A214" s="4">
         <v>40</v>
       </c>
@@ -9480,7 +9496,7 @@
       </c>
       <c r="L214" s="8"/>
     </row>
-    <row r="215" spans="1:12" ht="26.4">
+    <row r="215" spans="1:12" ht="26.4" hidden="1">
       <c r="A215" s="4">
         <v>41</v>
       </c>
@@ -9517,7 +9533,7 @@
       </c>
       <c r="L215" s="8"/>
     </row>
-    <row r="216" spans="1:12" ht="26.4">
+    <row r="216" spans="1:12" ht="26.4" hidden="1">
       <c r="A216" s="4">
         <v>42</v>
       </c>
@@ -9554,7 +9570,7 @@
       </c>
       <c r="L216" s="8"/>
     </row>
-    <row r="217" spans="1:12" ht="26.4">
+    <row r="217" spans="1:12" ht="26.4" hidden="1">
       <c r="A217" s="4">
         <v>43</v>
       </c>
@@ -9591,7 +9607,7 @@
       </c>
       <c r="L217" s="8"/>
     </row>
-    <row r="218" spans="1:12" ht="26.4">
+    <row r="218" spans="1:12" ht="26.4" hidden="1">
       <c r="A218" s="4">
         <v>44</v>
       </c>
@@ -9628,7 +9644,7 @@
       </c>
       <c r="L218" s="8"/>
     </row>
-    <row r="219" spans="1:12" ht="26.4">
+    <row r="219" spans="1:12" ht="26.4" hidden="1">
       <c r="A219" s="4">
         <v>45</v>
       </c>
@@ -9665,7 +9681,7 @@
       </c>
       <c r="L219" s="8"/>
     </row>
-    <row r="220" spans="1:12" ht="39.6">
+    <row r="220" spans="1:12" ht="39.6" hidden="1" customHeight="1">
       <c r="A220" s="4">
         <v>46</v>
       </c>
@@ -9702,7 +9718,7 @@
       </c>
       <c r="L220" s="8"/>
     </row>
-    <row r="221" spans="1:12" ht="52.8">
+    <row r="221" spans="1:12" ht="52.8" hidden="1">
       <c r="A221" s="4">
         <v>47</v>
       </c>
@@ -9739,7 +9755,7 @@
       </c>
       <c r="L221" s="8"/>
     </row>
-    <row r="222" spans="1:12" ht="26.4">
+    <row r="222" spans="1:12" ht="26.4" hidden="1">
       <c r="A222" s="4">
         <v>48</v>
       </c>
@@ -9776,7 +9792,7 @@
       </c>
       <c r="L222" s="8"/>
     </row>
-    <row r="223" spans="1:12" ht="26.4">
+    <row r="223" spans="1:12" ht="26.4" hidden="1">
       <c r="A223" s="4">
         <v>49</v>
       </c>
@@ -9813,7 +9829,7 @@
       </c>
       <c r="L223" s="8"/>
     </row>
-    <row r="224" spans="1:12" ht="26.4">
+    <row r="224" spans="1:12" ht="26.4" hidden="1">
       <c r="A224" s="4">
         <v>50</v>
       </c>
@@ -9850,7 +9866,7 @@
       </c>
       <c r="L224" s="8"/>
     </row>
-    <row r="225" spans="1:12" ht="26.4">
+    <row r="225" spans="1:12" ht="26.4" hidden="1">
       <c r="A225" s="4">
         <v>51</v>
       </c>
@@ -9887,7 +9903,7 @@
       </c>
       <c r="L225" s="8"/>
     </row>
-    <row r="226" spans="1:12" ht="26.4">
+    <row r="226" spans="1:12" ht="26.4" hidden="1">
       <c r="A226" s="4">
         <v>52</v>
       </c>
@@ -9924,7 +9940,7 @@
       </c>
       <c r="L226" s="8"/>
     </row>
-    <row r="227" spans="1:12" ht="26.4">
+    <row r="227" spans="1:12" ht="26.4" hidden="1">
       <c r="A227" s="4">
         <v>53</v>
       </c>
@@ -9961,7 +9977,7 @@
       </c>
       <c r="L227" s="8"/>
     </row>
-    <row r="228" spans="1:12" ht="26.4">
+    <row r="228" spans="1:12" ht="26.4" hidden="1">
       <c r="A228" s="4">
         <v>54</v>
       </c>
@@ -9998,7 +10014,7 @@
       </c>
       <c r="L228" s="8"/>
     </row>
-    <row r="229" spans="1:12" ht="26.4">
+    <row r="229" spans="1:12" ht="26.4" hidden="1">
       <c r="A229" s="4">
         <v>55</v>
       </c>
@@ -10035,7 +10051,7 @@
       </c>
       <c r="L229" s="8"/>
     </row>
-    <row r="230" spans="1:12" ht="26.4">
+    <row r="230" spans="1:12" ht="26.4" hidden="1">
       <c r="A230" s="4">
         <v>56</v>
       </c>
@@ -10072,7 +10088,7 @@
       </c>
       <c r="L230" s="8"/>
     </row>
-    <row r="231" spans="1:12" ht="26.4">
+    <row r="231" spans="1:12" ht="26.4" hidden="1">
       <c r="A231" s="4">
         <v>57</v>
       </c>
@@ -10109,7 +10125,7 @@
       </c>
       <c r="L231" s="8"/>
     </row>
-    <row r="232" spans="1:12" ht="26.4">
+    <row r="232" spans="1:12" ht="26.4" hidden="1">
       <c r="A232" s="4">
         <v>58</v>
       </c>
@@ -10146,7 +10162,7 @@
       </c>
       <c r="L232" s="8"/>
     </row>
-    <row r="233" spans="1:12" ht="26.4">
+    <row r="233" spans="1:12" ht="26.4" hidden="1">
       <c r="A233" s="4">
         <v>59</v>
       </c>
@@ -10183,7 +10199,7 @@
       </c>
       <c r="L233" s="8"/>
     </row>
-    <row r="234" spans="1:12" ht="39.6">
+    <row r="234" spans="1:12" ht="39.6" hidden="1" customHeight="1">
       <c r="A234" s="4">
         <v>60</v>
       </c>
@@ -10220,7 +10236,7 @@
       </c>
       <c r="L234" s="8"/>
     </row>
-    <row r="235" spans="1:12" ht="52.8">
+    <row r="235" spans="1:12" ht="52.8" hidden="1">
       <c r="A235" s="4">
         <v>61</v>
       </c>
@@ -10257,7 +10273,7 @@
       </c>
       <c r="L235" s="8"/>
     </row>
-    <row r="236" spans="1:12" ht="26.4">
+    <row r="236" spans="1:12" ht="26.4" hidden="1">
       <c r="A236" s="4">
         <v>62</v>
       </c>
@@ -10294,7 +10310,7 @@
       </c>
       <c r="L236" s="8"/>
     </row>
-    <row r="237" spans="1:12" ht="26.4">
+    <row r="237" spans="1:12" ht="26.4" hidden="1">
       <c r="A237" s="4">
         <v>63</v>
       </c>
@@ -10331,7 +10347,7 @@
       </c>
       <c r="L237" s="8"/>
     </row>
-    <row r="238" spans="1:12" ht="26.4">
+    <row r="238" spans="1:12" ht="26.4" hidden="1">
       <c r="A238" s="4">
         <v>64</v>
       </c>
@@ -10368,7 +10384,7 @@
       </c>
       <c r="L238" s="8"/>
     </row>
-    <row r="239" spans="1:12" ht="26.4">
+    <row r="239" spans="1:12" ht="26.4" hidden="1">
       <c r="A239" s="4">
         <v>65</v>
       </c>
@@ -10405,7 +10421,7 @@
       </c>
       <c r="L239" s="8"/>
     </row>
-    <row r="240" spans="1:12" ht="26.4">
+    <row r="240" spans="1:12" ht="26.4" hidden="1">
       <c r="A240" s="4">
         <v>66</v>
       </c>
@@ -10442,7 +10458,7 @@
       </c>
       <c r="L240" s="8"/>
     </row>
-    <row r="241" spans="1:12" ht="26.4">
+    <row r="241" spans="1:12" ht="26.4" hidden="1">
       <c r="A241" s="4">
         <v>67</v>
       </c>
@@ -10479,7 +10495,7 @@
       </c>
       <c r="L241" s="8"/>
     </row>
-    <row r="242" spans="1:12" ht="39.6">
+    <row r="242" spans="1:12" ht="39.6" hidden="1">
       <c r="A242" s="4">
         <v>68</v>
       </c>
@@ -10516,7 +10532,7 @@
       </c>
       <c r="L242" s="8"/>
     </row>
-    <row r="243" spans="1:12" ht="39.6">
+    <row r="243" spans="1:12" ht="39.6" hidden="1">
       <c r="A243" s="4">
         <v>69</v>
       </c>
@@ -10553,7 +10569,7 @@
       </c>
       <c r="L243" s="8"/>
     </row>
-    <row r="244" spans="1:12" ht="39.6">
+    <row r="244" spans="1:12" ht="39.6" hidden="1">
       <c r="A244" s="4">
         <v>70</v>
       </c>
@@ -10590,7 +10606,7 @@
       </c>
       <c r="L244" s="8"/>
     </row>
-    <row r="245" spans="1:12" ht="39.6">
+    <row r="245" spans="1:12" ht="39.6" hidden="1">
       <c r="A245" s="4">
         <v>71</v>
       </c>
@@ -10627,7 +10643,7 @@
       </c>
       <c r="L245" s="8"/>
     </row>
-    <row r="246" spans="1:12" ht="39.6">
+    <row r="246" spans="1:12" ht="39.6" hidden="1">
       <c r="A246" s="4">
         <v>72</v>
       </c>
@@ -10664,7 +10680,7 @@
       </c>
       <c r="L246" s="8"/>
     </row>
-    <row r="247" spans="1:12" ht="39.6">
+    <row r="247" spans="1:12" ht="39.6" hidden="1">
       <c r="A247" s="4">
         <v>73</v>
       </c>
@@ -10701,7 +10717,7 @@
       </c>
       <c r="L247" s="8"/>
     </row>
-    <row r="248" spans="1:12" ht="39.6">
+    <row r="248" spans="1:12" ht="39.6" hidden="1">
       <c r="A248" s="4">
         <v>74</v>
       </c>
@@ -10738,7 +10754,7 @@
       </c>
       <c r="L248" s="8"/>
     </row>
-    <row r="249" spans="1:12" ht="39.6">
+    <row r="249" spans="1:12" ht="39.6" hidden="1">
       <c r="A249" s="4">
         <v>75</v>
       </c>
@@ -10775,7 +10791,7 @@
       </c>
       <c r="L249" s="8"/>
     </row>
-    <row r="250" spans="1:12" ht="39.6">
+    <row r="250" spans="1:12" ht="39.6" hidden="1">
       <c r="A250" s="4">
         <v>76</v>
       </c>
@@ -10812,7 +10828,7 @@
       </c>
       <c r="L250" s="8"/>
     </row>
-    <row r="251" spans="1:12" ht="39.6">
+    <row r="251" spans="1:12" ht="39.6" hidden="1">
       <c r="A251" s="4">
         <v>77</v>
       </c>
@@ -10849,7 +10865,7 @@
       </c>
       <c r="L251" s="8"/>
     </row>
-    <row r="252" spans="1:12" ht="39.6">
+    <row r="252" spans="1:12" ht="39.6" hidden="1">
       <c r="A252" s="4">
         <v>78</v>
       </c>
@@ -10886,7 +10902,7 @@
       </c>
       <c r="L252" s="8"/>
     </row>
-    <row r="253" spans="1:12" ht="39.6">
+    <row r="253" spans="1:12" ht="39.6" hidden="1">
       <c r="A253" s="4">
         <v>79</v>
       </c>
@@ -10923,7 +10939,7 @@
       </c>
       <c r="L253" s="8"/>
     </row>
-    <row r="254" spans="1:12">
+    <row r="254" spans="1:12" hidden="1">
       <c r="A254" s="4">
         <v>80</v>
       </c>
@@ -10960,7 +10976,7 @@
       </c>
       <c r="L254" s="8"/>
     </row>
-    <row r="255" spans="1:12">
+    <row r="255" spans="1:12" hidden="1">
       <c r="A255" s="4">
         <v>81</v>
       </c>
@@ -10997,7 +11013,7 @@
       </c>
       <c r="L255" s="8"/>
     </row>
-    <row r="256" spans="1:12">
+    <row r="256" spans="1:12" hidden="1">
       <c r="A256" s="4">
         <v>82</v>
       </c>
@@ -11034,7 +11050,7 @@
       </c>
       <c r="L256" s="8"/>
     </row>
-    <row r="257" spans="1:12">
+    <row r="257" spans="1:12" hidden="1">
       <c r="A257" s="4">
         <v>83</v>
       </c>
@@ -11071,7 +11087,7 @@
       </c>
       <c r="L257" s="8"/>
     </row>
-    <row r="258" spans="1:12">
+    <row r="258" spans="1:12" hidden="1">
       <c r="A258" s="4">
         <v>84</v>
       </c>
@@ -11108,7 +11124,7 @@
       </c>
       <c r="L258" s="8"/>
     </row>
-    <row r="259" spans="1:12">
+    <row r="259" spans="1:12" hidden="1">
       <c r="A259" s="4">
         <v>85</v>
       </c>
@@ -11145,7 +11161,7 @@
       </c>
       <c r="L259" s="8"/>
     </row>
-    <row r="260" spans="1:12">
+    <row r="260" spans="1:12" hidden="1">
       <c r="A260" s="4">
         <v>86</v>
       </c>
@@ -11182,7 +11198,7 @@
       </c>
       <c r="L260" s="8"/>
     </row>
-    <row r="261" spans="1:12">
+    <row r="261" spans="1:12" hidden="1">
       <c r="A261" s="4">
         <v>87</v>
       </c>
@@ -11219,7 +11235,7 @@
       </c>
       <c r="L261" s="8"/>
     </row>
-    <row r="262" spans="1:12" ht="26.4">
+    <row r="262" spans="1:12" ht="26.4" hidden="1">
       <c r="A262" s="4">
         <v>88</v>
       </c>
@@ -11256,7 +11272,7 @@
       </c>
       <c r="L262" s="8"/>
     </row>
-    <row r="263" spans="1:12" ht="39.6">
+    <row r="263" spans="1:12" ht="39.6" hidden="1" customHeight="1">
       <c r="A263" s="4">
         <v>89</v>
       </c>
@@ -11293,7 +11309,7 @@
       </c>
       <c r="L263" s="8"/>
     </row>
-    <row r="264" spans="1:12" ht="52.8">
+    <row r="264" spans="1:12" ht="52.8" hidden="1">
       <c r="A264" s="4">
         <v>90</v>
       </c>
@@ -11330,7 +11346,7 @@
       </c>
       <c r="L264" s="8"/>
     </row>
-    <row r="265" spans="1:12">
+    <row r="265" spans="1:12" hidden="1">
       <c r="A265" s="4">
         <v>91</v>
       </c>
@@ -11367,7 +11383,7 @@
       </c>
       <c r="L265" s="8"/>
     </row>
-    <row r="266" spans="1:12">
+    <row r="266" spans="1:12" hidden="1">
       <c r="A266" s="4">
         <v>92</v>
       </c>
@@ -11404,7 +11420,7 @@
       </c>
       <c r="L266" s="8"/>
     </row>
-    <row r="267" spans="1:12">
+    <row r="267" spans="1:12" hidden="1">
       <c r="A267" s="4">
         <v>93</v>
       </c>
@@ -11441,7 +11457,7 @@
       </c>
       <c r="L267" s="8"/>
     </row>
-    <row r="268" spans="1:12" ht="39.6">
+    <row r="268" spans="1:12" ht="39.6" hidden="1">
       <c r="A268" s="4">
         <v>94</v>
       </c>
@@ -11478,7 +11494,7 @@
       </c>
       <c r="L268" s="8"/>
     </row>
-    <row r="269" spans="1:12" ht="26.4">
+    <row r="269" spans="1:12" ht="26.4" hidden="1">
       <c r="A269" s="4">
         <v>95</v>
       </c>
@@ -11515,7 +11531,7 @@
       </c>
       <c r="L269" s="8"/>
     </row>
-    <row r="270" spans="1:12" ht="39.6">
+    <row r="270" spans="1:12" ht="39.6" hidden="1">
       <c r="A270" s="4">
         <v>96</v>
       </c>
@@ -11552,7 +11568,7 @@
       </c>
       <c r="L270" s="8"/>
     </row>
-    <row r="271" spans="1:12" ht="26.4">
+    <row r="271" spans="1:12" ht="26.4" hidden="1">
       <c r="A271" s="4">
         <v>97</v>
       </c>
@@ -11589,7 +11605,7 @@
       </c>
       <c r="L271" s="8"/>
     </row>
-    <row r="272" spans="1:12" ht="39.6">
+    <row r="272" spans="1:12" ht="39.6" hidden="1">
       <c r="A272" s="4">
         <v>98</v>
       </c>
@@ -11626,7 +11642,7 @@
       </c>
       <c r="L272" s="8"/>
     </row>
-    <row r="273" spans="1:12" ht="26.4">
+    <row r="273" spans="1:12" ht="26.4" hidden="1">
       <c r="A273" s="4">
         <v>99</v>
       </c>
@@ -11663,7 +11679,7 @@
       </c>
       <c r="L273" s="8"/>
     </row>
-    <row r="274" spans="1:12" ht="39.6">
+    <row r="274" spans="1:12" ht="39.6" hidden="1">
       <c r="A274" s="4">
         <v>100</v>
       </c>
@@ -11700,7 +11716,7 @@
       </c>
       <c r="L274" s="8"/>
     </row>
-    <row r="275" spans="1:12" ht="26.4">
+    <row r="275" spans="1:12" ht="26.4" hidden="1">
       <c r="A275" s="4">
         <v>101</v>
       </c>
@@ -11737,7 +11753,7 @@
       </c>
       <c r="L275" s="8"/>
     </row>
-    <row r="276" spans="1:12" ht="39.6">
+    <row r="276" spans="1:12" ht="39.6" hidden="1">
       <c r="A276" s="4">
         <v>102</v>
       </c>
@@ -11774,7 +11790,7 @@
       </c>
       <c r="L276" s="8"/>
     </row>
-    <row r="277" spans="1:12" ht="26.4">
+    <row r="277" spans="1:12" ht="26.4" hidden="1">
       <c r="A277" s="4">
         <v>103</v>
       </c>
@@ -11811,7 +11827,7 @@
       </c>
       <c r="L277" s="8"/>
     </row>
-    <row r="278" spans="1:12" ht="26.4">
+    <row r="278" spans="1:12" ht="26.4" hidden="1">
       <c r="A278" s="4">
         <v>104</v>
       </c>
@@ -11848,7 +11864,7 @@
       </c>
       <c r="L278" s="8"/>
     </row>
-    <row r="279" spans="1:12" ht="39.6">
+    <row r="279" spans="1:12" ht="39.6" hidden="1">
       <c r="A279" s="4">
         <v>105</v>
       </c>
@@ -11885,7 +11901,7 @@
       </c>
       <c r="L279" s="8"/>
     </row>
-    <row r="280" spans="1:12" ht="39.6">
+    <row r="280" spans="1:12" ht="39.6" hidden="1">
       <c r="A280" s="4">
         <v>106</v>
       </c>
@@ -11922,7 +11938,7 @@
       </c>
       <c r="L280" s="8"/>
     </row>
-    <row r="281" spans="1:12" ht="39.6">
+    <row r="281" spans="1:12" ht="39.6" hidden="1">
       <c r="A281" s="4">
         <v>107</v>
       </c>
@@ -11959,7 +11975,7 @@
       </c>
       <c r="L281" s="8"/>
     </row>
-    <row r="282" spans="1:12" ht="39.6">
+    <row r="282" spans="1:12" ht="39.6" hidden="1">
       <c r="A282" s="4">
         <v>108</v>
       </c>
@@ -11996,7 +12012,7 @@
       </c>
       <c r="L282" s="8"/>
     </row>
-    <row r="283" spans="1:12" ht="39.6">
+    <row r="283" spans="1:12" ht="39.6" hidden="1">
       <c r="A283" s="4">
         <v>109</v>
       </c>
@@ -12033,7 +12049,7 @@
       </c>
       <c r="L283" s="8"/>
     </row>
-    <row r="284" spans="1:12" ht="26.4">
+    <row r="284" spans="1:12" ht="26.4" hidden="1">
       <c r="A284" s="4">
         <v>110</v>
       </c>
@@ -12070,7 +12086,7 @@
       </c>
       <c r="L284" s="8"/>
     </row>
-    <row r="285" spans="1:12" ht="39.6">
+    <row r="285" spans="1:12" ht="39.6" hidden="1">
       <c r="A285" s="4">
         <v>111</v>
       </c>
@@ -12107,7 +12123,7 @@
       </c>
       <c r="L285" s="8"/>
     </row>
-    <row r="286" spans="1:12" ht="39.6">
+    <row r="286" spans="1:12" ht="39.6" hidden="1">
       <c r="A286" s="4">
         <v>112</v>
       </c>
@@ -12144,7 +12160,7 @@
       </c>
       <c r="L286" s="8"/>
     </row>
-    <row r="287" spans="1:12" ht="39.6">
+    <row r="287" spans="1:12" ht="39.6" hidden="1">
       <c r="A287" s="4">
         <v>113</v>
       </c>
@@ -12179,7 +12195,7 @@
       </c>
       <c r="L287" s="8"/>
     </row>
-    <row r="288" spans="1:12" ht="39.6">
+    <row r="288" spans="1:12" ht="39.6" hidden="1">
       <c r="A288" s="4">
         <v>114</v>
       </c>
@@ -12214,7 +12230,7 @@
       </c>
       <c r="L288" s="8"/>
     </row>
-    <row r="289" spans="1:244" ht="26.4">
+    <row r="289" spans="1:244" ht="26.4" hidden="1">
       <c r="A289" s="4">
         <v>117</v>
       </c>
@@ -12251,7 +12267,7 @@
       </c>
       <c r="L289" s="8"/>
     </row>
-    <row r="290" spans="1:244" ht="39.6">
+    <row r="290" spans="1:244" ht="39.6" hidden="1">
       <c r="A290" s="4">
         <v>118</v>
       </c>
@@ -12288,7 +12304,7 @@
       </c>
       <c r="L290" s="8"/>
     </row>
-    <row r="291" spans="1:244" ht="26.4">
+    <row r="291" spans="1:244" ht="26.4" hidden="1">
       <c r="A291" s="4">
         <v>119</v>
       </c>
@@ -12325,7 +12341,7 @@
       </c>
       <c r="L291" s="8"/>
     </row>
-    <row r="292" spans="1:244" ht="39.6">
+    <row r="292" spans="1:244" ht="39.6" hidden="1">
       <c r="A292" s="4">
         <v>120</v>
       </c>
@@ -12362,7 +12378,7 @@
       </c>
       <c r="L292" s="8"/>
     </row>
-    <row r="293" spans="1:244" ht="26.4">
+    <row r="293" spans="1:244" ht="26.4" hidden="1">
       <c r="A293" s="4">
         <v>121</v>
       </c>
@@ -12399,7 +12415,7 @@
       </c>
       <c r="L293" s="8"/>
     </row>
-    <row r="294" spans="1:244">
+    <row r="294" spans="1:244" hidden="1">
       <c r="A294" s="4">
         <v>122</v>
       </c>
@@ -12436,7 +12452,7 @@
       </c>
       <c r="L294" s="8"/>
     </row>
-    <row r="295" spans="1:244" ht="26.4">
+    <row r="295" spans="1:244" ht="26.4" hidden="1">
       <c r="A295" s="4">
         <v>123</v>
       </c>
@@ -12473,7 +12489,7 @@
       </c>
       <c r="L295" s="8"/>
     </row>
-    <row r="296" spans="1:244" ht="26.4">
+    <row r="296" spans="1:244" ht="26.4" hidden="1">
       <c r="A296" s="4">
         <v>124</v>
       </c>
@@ -12510,7 +12526,7 @@
       </c>
       <c r="L296" s="8"/>
     </row>
-    <row r="297" spans="1:244" ht="39.6">
+    <row r="297" spans="1:244" ht="39.6" hidden="1">
       <c r="A297" s="4">
         <v>125</v>
       </c>
@@ -12547,7 +12563,7 @@
       </c>
       <c r="L297" s="8"/>
     </row>
-    <row r="298" spans="1:244" ht="26.4">
+    <row r="298" spans="1:244" ht="26.4" hidden="1">
       <c r="A298" s="4">
         <v>126</v>
       </c>
@@ -12584,7 +12600,7 @@
       </c>
       <c r="L298" s="8"/>
     </row>
-    <row r="299" spans="1:244" ht="26.4">
+    <row r="299" spans="1:244" ht="26.4" hidden="1">
       <c r="A299" s="4">
         <v>127</v>
       </c>
@@ -12621,7 +12637,7 @@
       </c>
       <c r="L299" s="8"/>
     </row>
-    <row r="300" spans="1:244" ht="26.4">
+    <row r="300" spans="1:244" ht="26.4" hidden="1">
       <c r="A300" s="4">
         <v>128</v>
       </c>
@@ -12658,7 +12674,7 @@
       </c>
       <c r="L300" s="8"/>
     </row>
-    <row r="301" spans="1:244" ht="26.4">
+    <row r="301" spans="1:244" ht="26.4" hidden="1">
       <c r="A301" s="4">
         <v>129</v>
       </c>
@@ -12695,7 +12711,7 @@
       </c>
       <c r="L301" s="8"/>
     </row>
-    <row r="302" spans="1:244" ht="26.4">
+    <row r="302" spans="1:244" ht="26.4" hidden="1">
       <c r="A302" s="4">
         <v>130</v>
       </c>
@@ -12732,7 +12748,7 @@
       </c>
       <c r="L302" s="29"/>
     </row>
-    <row r="303" spans="1:244" s="9" customFormat="1" ht="26.4">
+    <row r="303" spans="1:244" s="9" customFormat="1" ht="26.4" hidden="1">
       <c r="A303" s="4">
         <v>131</v>
       </c>
@@ -13001,7 +13017,7 @@
       <c r="II303"/>
       <c r="IJ303" s="54"/>
     </row>
-    <row r="304" spans="1:244" ht="26.4">
+    <row r="304" spans="1:244" ht="26.4" hidden="1">
       <c r="A304" s="4">
         <v>132</v>
       </c>
@@ -13038,7 +13054,7 @@
       </c>
       <c r="L304" s="8"/>
     </row>
-    <row r="305" spans="1:12" ht="26.4">
+    <row r="305" spans="1:12" ht="26.4" hidden="1">
       <c r="A305" s="4">
         <v>133</v>
       </c>
@@ -13075,7 +13091,7 @@
       </c>
       <c r="L305" s="8"/>
     </row>
-    <row r="306" spans="1:12" ht="26.4">
+    <row r="306" spans="1:12" ht="26.4" hidden="1">
       <c r="A306" s="4">
         <v>134</v>
       </c>
@@ -13112,25 +13128,25 @@
       </c>
       <c r="L306" s="8"/>
     </row>
-    <row r="307" spans="1:12" ht="21" customHeight="1">
+    <row r="307" spans="1:12" ht="21" hidden="1" customHeight="1">
       <c r="A307" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B307" s="119"/>
-      <c r="C307" s="120"/>
-      <c r="D307" s="120"/>
-      <c r="E307" s="120"/>
-      <c r="F307" s="120"/>
-      <c r="G307" s="120"/>
-      <c r="H307" s="120"/>
-      <c r="I307" s="120"/>
-      <c r="J307" s="121"/>
+      <c r="B307" s="63"/>
+      <c r="C307" s="82"/>
+      <c r="D307" s="82"/>
+      <c r="E307" s="82"/>
+      <c r="F307" s="82"/>
+      <c r="G307" s="82"/>
+      <c r="H307" s="82"/>
+      <c r="I307" s="82"/>
+      <c r="J307" s="66"/>
       <c r="K307" s="12">
         <v>1594003.1</v>
       </c>
       <c r="L307" s="14"/>
     </row>
-    <row r="308" spans="1:12">
+    <row r="308" spans="1:12" hidden="1">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -13144,7 +13160,7 @@
       <c r="K308" s="1"/>
       <c r="L308" s="1"/>
     </row>
-    <row r="309" spans="1:12" ht="26.4">
+    <row r="309" spans="1:12" ht="26.4" hidden="1">
       <c r="A309" s="1"/>
       <c r="B309" s="3" t="s">
         <v>12</v>
@@ -13180,7 +13196,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="26.4">
+    <row r="310" spans="1:12" ht="26.4" hidden="1">
       <c r="A310" s="3" t="s">
         <v>11</v>
       </c>
@@ -13217,7 +13233,7 @@
       </c>
       <c r="L310" s="8"/>
     </row>
-    <row r="311" spans="1:12" ht="26.4">
+    <row r="311" spans="1:12" ht="26.4" hidden="1">
       <c r="A311" s="4">
         <v>1</v>
       </c>
@@ -13254,7 +13270,7 @@
       </c>
       <c r="L311" s="8"/>
     </row>
-    <row r="312" spans="1:12" ht="26.4">
+    <row r="312" spans="1:12" ht="26.4" hidden="1">
       <c r="A312" s="4">
         <v>2</v>
       </c>
@@ -13291,7 +13307,7 @@
       </c>
       <c r="L312" s="8"/>
     </row>
-    <row r="313" spans="1:12" ht="26.4">
+    <row r="313" spans="1:12" ht="26.4" hidden="1">
       <c r="A313" s="4">
         <v>3</v>
       </c>
@@ -13328,7 +13344,7 @@
       </c>
       <c r="L313" s="8"/>
     </row>
-    <row r="314" spans="1:12" ht="26.4">
+    <row r="314" spans="1:12" ht="26.4" hidden="1">
       <c r="A314" s="4">
         <v>4</v>
       </c>
@@ -13365,7 +13381,7 @@
       </c>
       <c r="L314" s="8"/>
     </row>
-    <row r="315" spans="1:12" ht="26.4">
+    <row r="315" spans="1:12" ht="26.4" hidden="1">
       <c r="A315" s="4">
         <v>5</v>
       </c>
@@ -13402,7 +13418,7 @@
       </c>
       <c r="L315" s="8"/>
     </row>
-    <row r="316" spans="1:12" ht="26.4">
+    <row r="316" spans="1:12" ht="26.4" hidden="1">
       <c r="A316" s="4">
         <v>6</v>
       </c>
@@ -13439,7 +13455,7 @@
       </c>
       <c r="L316" s="8"/>
     </row>
-    <row r="317" spans="1:12" ht="26.4">
+    <row r="317" spans="1:12" ht="26.4" hidden="1">
       <c r="A317" s="4">
         <v>7</v>
       </c>
@@ -13476,7 +13492,7 @@
       </c>
       <c r="L317" s="8"/>
     </row>
-    <row r="318" spans="1:12" ht="26.4">
+    <row r="318" spans="1:12" ht="26.4" hidden="1">
       <c r="A318" s="4">
         <v>8</v>
       </c>
@@ -13513,7 +13529,7 @@
       </c>
       <c r="L318" s="8"/>
     </row>
-    <row r="319" spans="1:12" ht="26.4">
+    <row r="319" spans="1:12" ht="26.4" hidden="1">
       <c r="A319" s="4">
         <v>9</v>
       </c>
@@ -13550,7 +13566,7 @@
       </c>
       <c r="L319" s="8"/>
     </row>
-    <row r="320" spans="1:12" ht="26.4">
+    <row r="320" spans="1:12" ht="26.4" hidden="1">
       <c r="A320" s="4">
         <v>10</v>
       </c>
@@ -13587,7 +13603,7 @@
       </c>
       <c r="L320" s="8"/>
     </row>
-    <row r="321" spans="1:12" ht="26.4">
+    <row r="321" spans="1:12" ht="26.4" hidden="1">
       <c r="A321" s="4">
         <v>11</v>
       </c>
@@ -13624,7 +13640,7 @@
       </c>
       <c r="L321" s="8"/>
     </row>
-    <row r="322" spans="1:12" ht="26.4">
+    <row r="322" spans="1:12" ht="26.4" hidden="1">
       <c r="A322" s="4">
         <v>12</v>
       </c>
@@ -13661,7 +13677,7 @@
       </c>
       <c r="L322" s="8"/>
     </row>
-    <row r="323" spans="1:12" ht="26.4">
+    <row r="323" spans="1:12" ht="26.4" hidden="1">
       <c r="A323" s="4">
         <v>13</v>
       </c>
@@ -13698,7 +13714,7 @@
       </c>
       <c r="L323" s="8"/>
     </row>
-    <row r="324" spans="1:12" ht="26.4">
+    <row r="324" spans="1:12" ht="26.4" hidden="1">
       <c r="A324" s="4">
         <v>14</v>
       </c>
@@ -13735,7 +13751,7 @@
       </c>
       <c r="L324" s="8"/>
     </row>
-    <row r="325" spans="1:12" ht="26.4">
+    <row r="325" spans="1:12" ht="26.4" hidden="1">
       <c r="A325" s="4">
         <v>15</v>
       </c>
@@ -13772,7 +13788,7 @@
       </c>
       <c r="L325" s="8"/>
     </row>
-    <row r="326" spans="1:12" ht="26.4">
+    <row r="326" spans="1:12" ht="26.4" hidden="1">
       <c r="A326" s="4">
         <v>16</v>
       </c>
@@ -13809,7 +13825,7 @@
       </c>
       <c r="L326" s="8"/>
     </row>
-    <row r="327" spans="1:12" ht="26.4">
+    <row r="327" spans="1:12" ht="26.4" hidden="1">
       <c r="A327" s="4">
         <v>17</v>
       </c>
@@ -13846,7 +13862,7 @@
       </c>
       <c r="L327" s="8"/>
     </row>
-    <row r="328" spans="1:12" ht="26.4">
+    <row r="328" spans="1:12" ht="26.4" hidden="1">
       <c r="A328" s="4">
         <v>18</v>
       </c>
@@ -13883,7 +13899,7 @@
       </c>
       <c r="L328" s="8"/>
     </row>
-    <row r="329" spans="1:12" ht="26.4">
+    <row r="329" spans="1:12" ht="26.4" hidden="1">
       <c r="A329" s="4">
         <v>19</v>
       </c>
@@ -13920,7 +13936,7 @@
       </c>
       <c r="L329" s="8"/>
     </row>
-    <row r="330" spans="1:12" ht="26.4">
+    <row r="330" spans="1:12" ht="26.4" hidden="1">
       <c r="A330" s="4">
         <v>20</v>
       </c>
@@ -13957,7 +13973,7 @@
       </c>
       <c r="L330" s="8"/>
     </row>
-    <row r="331" spans="1:12" ht="26.4">
+    <row r="331" spans="1:12" ht="26.4" hidden="1">
       <c r="A331" s="4">
         <v>21</v>
       </c>
@@ -13994,7 +14010,7 @@
       </c>
       <c r="L331" s="8"/>
     </row>
-    <row r="332" spans="1:12" ht="26.4">
+    <row r="332" spans="1:12" ht="26.4" hidden="1">
       <c r="A332" s="4">
         <v>22</v>
       </c>
@@ -14031,7 +14047,7 @@
       </c>
       <c r="L332" s="8"/>
     </row>
-    <row r="333" spans="1:12" ht="26.4">
+    <row r="333" spans="1:12" ht="26.4" hidden="1">
       <c r="A333" s="4">
         <v>23</v>
       </c>
@@ -14068,7 +14084,7 @@
       </c>
       <c r="L333" s="8"/>
     </row>
-    <row r="334" spans="1:12" ht="39.6">
+    <row r="334" spans="1:12" ht="39.6" hidden="1">
       <c r="A334" s="4">
         <v>24</v>
       </c>
@@ -14105,7 +14121,7 @@
       </c>
       <c r="L334" s="8"/>
     </row>
-    <row r="335" spans="1:12" ht="26.4">
+    <row r="335" spans="1:12" ht="26.4" hidden="1">
       <c r="A335" s="4">
         <v>25</v>
       </c>
@@ -14142,7 +14158,7 @@
       </c>
       <c r="L335" s="8"/>
     </row>
-    <row r="336" spans="1:12" ht="26.4">
+    <row r="336" spans="1:12" ht="26.4" hidden="1">
       <c r="A336" s="4">
         <v>26</v>
       </c>
@@ -14179,7 +14195,7 @@
       </c>
       <c r="L336" s="8"/>
     </row>
-    <row r="337" spans="1:12" ht="26.4">
+    <row r="337" spans="1:12" ht="26.4" hidden="1">
       <c r="A337" s="4">
         <v>27</v>
       </c>
@@ -14216,7 +14232,7 @@
       </c>
       <c r="L337" s="8"/>
     </row>
-    <row r="338" spans="1:12" ht="52.8">
+    <row r="338" spans="1:12" ht="52.8" hidden="1">
       <c r="A338" s="4">
         <v>28</v>
       </c>
@@ -14253,7 +14269,7 @@
       </c>
       <c r="L338" s="8"/>
     </row>
-    <row r="339" spans="1:12" ht="26.4">
+    <row r="339" spans="1:12" ht="26.4" hidden="1">
       <c r="A339" s="4">
         <v>29</v>
       </c>
@@ -14290,7 +14306,7 @@
       </c>
       <c r="L339" s="8"/>
     </row>
-    <row r="340" spans="1:12" ht="26.4">
+    <row r="340" spans="1:12" ht="26.4" hidden="1">
       <c r="A340" s="4">
         <v>30</v>
       </c>
@@ -14327,7 +14343,7 @@
       </c>
       <c r="L340" s="8"/>
     </row>
-    <row r="341" spans="1:12" ht="26.4">
+    <row r="341" spans="1:12" ht="26.4" hidden="1">
       <c r="A341" s="4">
         <v>31</v>
       </c>
@@ -14364,7 +14380,7 @@
       </c>
       <c r="L341" s="8"/>
     </row>
-    <row r="342" spans="1:12" ht="26.4">
+    <row r="342" spans="1:12" ht="26.4" hidden="1">
       <c r="A342" s="4">
         <v>32</v>
       </c>
@@ -14401,7 +14417,7 @@
       </c>
       <c r="L342" s="8"/>
     </row>
-    <row r="343" spans="1:12" ht="26.4">
+    <row r="343" spans="1:12" ht="26.4" hidden="1">
       <c r="A343" s="4">
         <v>33</v>
       </c>
@@ -14438,7 +14454,7 @@
       </c>
       <c r="L343" s="8"/>
     </row>
-    <row r="344" spans="1:12" ht="26.4">
+    <row r="344" spans="1:12" ht="26.4" hidden="1">
       <c r="A344" s="4">
         <v>34</v>
       </c>
@@ -14475,7 +14491,7 @@
       </c>
       <c r="L344" s="8"/>
     </row>
-    <row r="345" spans="1:12" ht="26.4">
+    <row r="345" spans="1:12" ht="26.4" hidden="1">
       <c r="A345" s="4">
         <v>35</v>
       </c>
@@ -14512,7 +14528,7 @@
       </c>
       <c r="L345" s="8"/>
     </row>
-    <row r="346" spans="1:12" ht="26.4">
+    <row r="346" spans="1:12" ht="26.4" hidden="1">
       <c r="A346" s="4">
         <v>36</v>
       </c>
@@ -14549,7 +14565,7 @@
       </c>
       <c r="L346" s="8"/>
     </row>
-    <row r="347" spans="1:12" ht="26.4">
+    <row r="347" spans="1:12" ht="26.4" hidden="1">
       <c r="A347" s="4">
         <v>37</v>
       </c>
@@ -14586,7 +14602,7 @@
       </c>
       <c r="L347" s="8"/>
     </row>
-    <row r="348" spans="1:12" ht="26.4">
+    <row r="348" spans="1:12" ht="26.4" hidden="1">
       <c r="A348" s="4">
         <v>38</v>
       </c>
@@ -14623,7 +14639,7 @@
       </c>
       <c r="L348" s="8"/>
     </row>
-    <row r="349" spans="1:12" ht="26.4">
+    <row r="349" spans="1:12" ht="26.4" hidden="1">
       <c r="A349" s="4">
         <v>39</v>
       </c>
@@ -14660,7 +14676,7 @@
       </c>
       <c r="L349" s="8"/>
     </row>
-    <row r="350" spans="1:12" ht="26.4">
+    <row r="350" spans="1:12" ht="26.4" hidden="1">
       <c r="A350" s="4">
         <v>40</v>
       </c>
@@ -14697,7 +14713,7 @@
       </c>
       <c r="L350" s="8"/>
     </row>
-    <row r="351" spans="1:12" ht="26.4">
+    <row r="351" spans="1:12" ht="26.4" hidden="1">
       <c r="A351" s="4">
         <v>41</v>
       </c>
@@ -14734,7 +14750,7 @@
       </c>
       <c r="L351" s="8"/>
     </row>
-    <row r="352" spans="1:12" ht="26.4">
+    <row r="352" spans="1:12" ht="26.4" hidden="1">
       <c r="A352" s="4">
         <v>42</v>
       </c>
@@ -14771,7 +14787,7 @@
       </c>
       <c r="L352" s="8"/>
     </row>
-    <row r="353" spans="1:12" ht="26.4">
+    <row r="353" spans="1:12" ht="26.4" hidden="1">
       <c r="A353" s="4">
         <v>43</v>
       </c>
@@ -14808,7 +14824,7 @@
       </c>
       <c r="L353" s="8"/>
     </row>
-    <row r="354" spans="1:12" ht="26.4">
+    <row r="354" spans="1:12" ht="26.4" hidden="1">
       <c r="A354" s="4">
         <v>44</v>
       </c>
@@ -14845,7 +14861,7 @@
       </c>
       <c r="L354" s="8"/>
     </row>
-    <row r="355" spans="1:12" ht="52.8">
+    <row r="355" spans="1:12" ht="52.8" hidden="1">
       <c r="A355" s="4">
         <v>45</v>
       </c>
@@ -14882,7 +14898,7 @@
       </c>
       <c r="L355" s="8"/>
     </row>
-    <row r="356" spans="1:12" ht="26.4">
+    <row r="356" spans="1:12" ht="26.4" hidden="1">
       <c r="A356" s="4">
         <v>46</v>
       </c>
@@ -14919,7 +14935,7 @@
       </c>
       <c r="L356" s="8"/>
     </row>
-    <row r="357" spans="1:12" ht="26.4">
+    <row r="357" spans="1:12" ht="26.4" hidden="1">
       <c r="A357" s="4">
         <v>47</v>
       </c>
@@ -14956,7 +14972,7 @@
       </c>
       <c r="L357" s="8"/>
     </row>
-    <row r="358" spans="1:12" ht="26.4">
+    <row r="358" spans="1:12" ht="26.4" hidden="1">
       <c r="A358" s="4">
         <v>48</v>
       </c>
@@ -14993,7 +15009,7 @@
       </c>
       <c r="L358" s="8"/>
     </row>
-    <row r="359" spans="1:12" ht="26.4">
+    <row r="359" spans="1:12" ht="26.4" hidden="1">
       <c r="A359" s="4">
         <v>49</v>
       </c>
@@ -15030,7 +15046,7 @@
       </c>
       <c r="L359" s="8"/>
     </row>
-    <row r="360" spans="1:12" ht="26.4">
+    <row r="360" spans="1:12" ht="26.4" hidden="1">
       <c r="A360" s="4">
         <v>50</v>
       </c>
@@ -15067,7 +15083,7 @@
       </c>
       <c r="L360" s="8"/>
     </row>
-    <row r="361" spans="1:12" ht="26.4">
+    <row r="361" spans="1:12" ht="26.4" hidden="1">
       <c r="A361" s="4">
         <v>51</v>
       </c>
@@ -15104,7 +15120,7 @@
       </c>
       <c r="L361" s="8"/>
     </row>
-    <row r="362" spans="1:12" ht="52.8">
+    <row r="362" spans="1:12" ht="52.8" hidden="1">
       <c r="A362" s="4">
         <v>52</v>
       </c>
@@ -15141,7 +15157,7 @@
       </c>
       <c r="L362" s="8"/>
     </row>
-    <row r="363" spans="1:12" ht="39.6">
+    <row r="363" spans="1:12" ht="39.6" hidden="1" customHeight="1">
       <c r="A363" s="4">
         <v>53</v>
       </c>
@@ -15178,7 +15194,7 @@
       </c>
       <c r="L363" s="8"/>
     </row>
-    <row r="364" spans="1:12" ht="26.4">
+    <row r="364" spans="1:12" ht="26.4" hidden="1">
       <c r="A364" s="4">
         <v>54</v>
       </c>
@@ -15215,7 +15231,7 @@
       </c>
       <c r="L364" s="8"/>
     </row>
-    <row r="365" spans="1:12" ht="26.4">
+    <row r="365" spans="1:12" ht="26.4" hidden="1">
       <c r="A365" s="4">
         <v>55</v>
       </c>
@@ -15252,7 +15268,7 @@
       </c>
       <c r="L365" s="8"/>
     </row>
-    <row r="366" spans="1:12" ht="26.4">
+    <row r="366" spans="1:12" ht="26.4" hidden="1">
       <c r="A366" s="4">
         <v>56</v>
       </c>
@@ -15289,7 +15305,7 @@
       </c>
       <c r="L366" s="8"/>
     </row>
-    <row r="367" spans="1:12" ht="26.4">
+    <row r="367" spans="1:12" ht="26.4" hidden="1">
       <c r="A367" s="4">
         <v>57</v>
       </c>
@@ -15326,7 +15342,7 @@
       </c>
       <c r="L367" s="8"/>
     </row>
-    <row r="368" spans="1:12" ht="26.4">
+    <row r="368" spans="1:12" ht="26.4" hidden="1">
       <c r="A368" s="4">
         <v>58</v>
       </c>
@@ -15363,7 +15379,7 @@
       </c>
       <c r="L368" s="8"/>
     </row>
-    <row r="369" spans="1:12" ht="52.8">
+    <row r="369" spans="1:12" ht="52.8" hidden="1">
       <c r="A369" s="4">
         <v>59</v>
       </c>
@@ -15400,7 +15416,7 @@
       </c>
       <c r="L369" s="8"/>
     </row>
-    <row r="370" spans="1:12" ht="52.8">
+    <row r="370" spans="1:12" ht="52.8" hidden="1">
       <c r="A370" s="4">
         <v>60</v>
       </c>
@@ -15437,7 +15453,7 @@
       </c>
       <c r="L370" s="8"/>
     </row>
-    <row r="371" spans="1:12" ht="26.4">
+    <row r="371" spans="1:12" ht="26.4" hidden="1">
       <c r="A371" s="4">
         <v>61</v>
       </c>
@@ -15474,7 +15490,7 @@
       </c>
       <c r="L371" s="8"/>
     </row>
-    <row r="372" spans="1:12" ht="39.6">
+    <row r="372" spans="1:12" ht="39.6" hidden="1">
       <c r="A372" s="4">
         <v>62</v>
       </c>
@@ -15511,7 +15527,7 @@
       </c>
       <c r="L372" s="8"/>
     </row>
-    <row r="373" spans="1:12" ht="39.6">
+    <row r="373" spans="1:12" ht="39.6" hidden="1">
       <c r="A373" s="4">
         <v>63</v>
       </c>
@@ -15548,7 +15564,7 @@
       </c>
       <c r="L373" s="8"/>
     </row>
-    <row r="374" spans="1:12" ht="39.6">
+    <row r="374" spans="1:12" ht="39.6" hidden="1">
       <c r="A374" s="4">
         <v>64</v>
       </c>
@@ -15585,7 +15601,7 @@
       </c>
       <c r="L374" s="8"/>
     </row>
-    <row r="375" spans="1:12" ht="39.6">
+    <row r="375" spans="1:12" ht="39.6" hidden="1">
       <c r="A375" s="4">
         <v>65</v>
       </c>
@@ -15622,7 +15638,7 @@
       </c>
       <c r="L375" s="8"/>
     </row>
-    <row r="376" spans="1:12" ht="39.6">
+    <row r="376" spans="1:12" ht="39.6" hidden="1">
       <c r="A376" s="4">
         <v>66</v>
       </c>
@@ -15696,7 +15712,7 @@
       </c>
       <c r="L377" s="8"/>
     </row>
-    <row r="378" spans="1:12" ht="39.6">
+    <row r="378" spans="1:12" ht="39.6" hidden="1">
       <c r="A378" s="4">
         <v>68</v>
       </c>
@@ -15733,7 +15749,7 @@
       </c>
       <c r="L378" s="8"/>
     </row>
-    <row r="379" spans="1:12" ht="39.6">
+    <row r="379" spans="1:12" ht="39.6" hidden="1">
       <c r="A379" s="4">
         <v>69</v>
       </c>
@@ -15844,7 +15860,7 @@
       </c>
       <c r="L381" s="8"/>
     </row>
-    <row r="382" spans="1:12" ht="39.6">
+    <row r="382" spans="1:12" ht="39.6" hidden="1">
       <c r="A382" s="4">
         <v>72</v>
       </c>
@@ -15881,7 +15897,7 @@
       </c>
       <c r="L382" s="8"/>
     </row>
-    <row r="383" spans="1:12" ht="39.6">
+    <row r="383" spans="1:12" ht="39.6" hidden="1">
       <c r="A383" s="4">
         <v>73</v>
       </c>
@@ -15918,7 +15934,7 @@
       </c>
       <c r="L383" s="8"/>
     </row>
-    <row r="384" spans="1:12" ht="39.6">
+    <row r="384" spans="1:12" ht="39.6" hidden="1">
       <c r="A384" s="4">
         <v>74</v>
       </c>
@@ -15955,7 +15971,7 @@
       </c>
       <c r="L384" s="8"/>
     </row>
-    <row r="385" spans="1:12" ht="39.6">
+    <row r="385" spans="1:12" ht="39.6" hidden="1">
       <c r="A385" s="4">
         <v>75</v>
       </c>
@@ -15992,7 +16008,7 @@
       </c>
       <c r="L385" s="8"/>
     </row>
-    <row r="386" spans="1:12" ht="39.6">
+    <row r="386" spans="1:12" ht="39.6" hidden="1">
       <c r="A386" s="4">
         <v>76</v>
       </c>
@@ -16029,7 +16045,7 @@
       </c>
       <c r="L386" s="8"/>
     </row>
-    <row r="387" spans="1:12" ht="39.6">
+    <row r="387" spans="1:12" ht="39.6" hidden="1">
       <c r="A387" s="4">
         <v>77</v>
       </c>
@@ -16066,7 +16082,7 @@
       </c>
       <c r="L387" s="8"/>
     </row>
-    <row r="388" spans="1:12" ht="39.6">
+    <row r="388" spans="1:12" ht="39.6" hidden="1">
       <c r="A388" s="4">
         <v>78</v>
       </c>
@@ -16103,7 +16119,7 @@
       </c>
       <c r="L388" s="8"/>
     </row>
-    <row r="389" spans="1:12">
+    <row r="389" spans="1:12" hidden="1">
       <c r="A389" s="4">
         <v>79</v>
       </c>
@@ -16140,7 +16156,7 @@
       </c>
       <c r="L389" s="8"/>
     </row>
-    <row r="390" spans="1:12">
+    <row r="390" spans="1:12" hidden="1">
       <c r="A390" s="4">
         <v>80</v>
       </c>
@@ -16177,7 +16193,7 @@
       </c>
       <c r="L390" s="8"/>
     </row>
-    <row r="391" spans="1:12">
+    <row r="391" spans="1:12" hidden="1">
       <c r="A391" s="4">
         <v>81</v>
       </c>
@@ -16214,7 +16230,7 @@
       </c>
       <c r="L391" s="8"/>
     </row>
-    <row r="392" spans="1:12">
+    <row r="392" spans="1:12" hidden="1">
       <c r="A392" s="4">
         <v>82</v>
       </c>
@@ -16251,7 +16267,7 @@
       </c>
       <c r="L392" s="8"/>
     </row>
-    <row r="393" spans="1:12">
+    <row r="393" spans="1:12" hidden="1">
       <c r="A393" s="4">
         <v>83</v>
       </c>
@@ -16288,7 +16304,7 @@
       </c>
       <c r="L393" s="8"/>
     </row>
-    <row r="394" spans="1:12">
+    <row r="394" spans="1:12" hidden="1">
       <c r="A394" s="4">
         <v>84</v>
       </c>
@@ -16325,7 +16341,7 @@
       </c>
       <c r="L394" s="8"/>
     </row>
-    <row r="395" spans="1:12">
+    <row r="395" spans="1:12" hidden="1">
       <c r="A395" s="4">
         <v>85</v>
       </c>
@@ -16362,7 +16378,7 @@
       </c>
       <c r="L395" s="8"/>
     </row>
-    <row r="396" spans="1:12">
+    <row r="396" spans="1:12" hidden="1">
       <c r="A396" s="4">
         <v>86</v>
       </c>
@@ -16399,7 +16415,7 @@
       </c>
       <c r="L396" s="8"/>
     </row>
-    <row r="397" spans="1:12">
+    <row r="397" spans="1:12" hidden="1">
       <c r="A397" s="4">
         <v>87</v>
       </c>
@@ -16436,7 +16452,7 @@
       </c>
       <c r="L397" s="8"/>
     </row>
-    <row r="398" spans="1:12">
+    <row r="398" spans="1:12" hidden="1">
       <c r="A398" s="4">
         <v>88</v>
       </c>
@@ -16473,7 +16489,7 @@
       </c>
       <c r="L398" s="8"/>
     </row>
-    <row r="399" spans="1:12">
+    <row r="399" spans="1:12" hidden="1">
       <c r="A399" s="4">
         <v>89</v>
       </c>
@@ -16510,7 +16526,7 @@
       </c>
       <c r="L399" s="8"/>
     </row>
-    <row r="400" spans="1:12" ht="26.4">
+    <row r="400" spans="1:12" ht="26.4" hidden="1">
       <c r="A400" s="4">
         <v>90</v>
       </c>
@@ -16547,7 +16563,7 @@
       </c>
       <c r="L400" s="8"/>
     </row>
-    <row r="401" spans="1:12">
+    <row r="401" spans="1:12" hidden="1">
       <c r="A401" s="4">
         <v>91</v>
       </c>
@@ -16584,7 +16600,7 @@
       </c>
       <c r="L401" s="8"/>
     </row>
-    <row r="402" spans="1:12">
+    <row r="402" spans="1:12" hidden="1">
       <c r="A402" s="4">
         <v>92</v>
       </c>
@@ -16621,7 +16637,7 @@
       </c>
       <c r="L402" s="8"/>
     </row>
-    <row r="403" spans="1:12">
+    <row r="403" spans="1:12" hidden="1">
       <c r="A403" s="4">
         <v>93</v>
       </c>
@@ -16658,7 +16674,7 @@
       </c>
       <c r="L403" s="8"/>
     </row>
-    <row r="404" spans="1:12" ht="26.4">
+    <row r="404" spans="1:12" ht="26.4" hidden="1">
       <c r="A404" s="4">
         <v>118</v>
       </c>
@@ -16695,7 +16711,7 @@
       </c>
       <c r="L404" s="8"/>
     </row>
-    <row r="405" spans="1:12" ht="52.8">
+    <row r="405" spans="1:12" ht="52.8" hidden="1">
       <c r="A405" s="4">
         <v>119</v>
       </c>
@@ -16732,7 +16748,7 @@
       </c>
       <c r="L405" s="8"/>
     </row>
-    <row r="406" spans="1:12" ht="26.4">
+    <row r="406" spans="1:12" ht="26.4" hidden="1">
       <c r="A406" s="4">
         <v>120</v>
       </c>
@@ -16769,7 +16785,7 @@
       </c>
       <c r="L406" s="8"/>
     </row>
-    <row r="407" spans="1:12" ht="26.4">
+    <row r="407" spans="1:12" ht="26.4" hidden="1">
       <c r="A407" s="4">
         <v>121</v>
       </c>
@@ -16806,7 +16822,7 @@
       </c>
       <c r="L407" s="8"/>
     </row>
-    <row r="408" spans="1:12" ht="26.4">
+    <row r="408" spans="1:12" ht="26.4" hidden="1">
       <c r="A408" s="4">
         <v>122</v>
       </c>
@@ -16843,7 +16859,7 @@
       </c>
       <c r="L408" s="8"/>
     </row>
-    <row r="409" spans="1:12" ht="26.4">
+    <row r="409" spans="1:12" ht="26.4" hidden="1">
       <c r="A409" s="4">
         <v>123</v>
       </c>
@@ -16880,7 +16896,7 @@
       </c>
       <c r="L409" s="8"/>
     </row>
-    <row r="410" spans="1:12">
+    <row r="410" spans="1:12" hidden="1">
       <c r="A410" s="4">
         <v>124</v>
       </c>
@@ -16913,7 +16929,7 @@
       </c>
       <c r="L410" s="8"/>
     </row>
-    <row r="411" spans="1:12">
+    <row r="411" spans="1:12" hidden="1">
       <c r="A411" s="4">
         <v>125</v>
       </c>
@@ -16948,26 +16964,26 @@
       </c>
       <c r="L411" s="8"/>
     </row>
-    <row r="412" spans="1:12" ht="40.200000000000003" customHeight="1">
+    <row r="412" spans="1:12" ht="40.200000000000003" hidden="1" customHeight="1">
       <c r="A412" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B412" s="119"/>
-      <c r="C412" s="120"/>
-      <c r="D412" s="120"/>
-      <c r="E412" s="120"/>
-      <c r="F412" s="120"/>
-      <c r="G412" s="120"/>
-      <c r="H412" s="120"/>
-      <c r="I412" s="120"/>
-      <c r="J412" s="121"/>
+      <c r="B412" s="63"/>
+      <c r="C412" s="82"/>
+      <c r="D412" s="82"/>
+      <c r="E412" s="82"/>
+      <c r="F412" s="82"/>
+      <c r="G412" s="82"/>
+      <c r="H412" s="82"/>
+      <c r="I412" s="82"/>
+      <c r="J412" s="66"/>
       <c r="K412" s="12">
         <f>SUM(K310:K411)</f>
         <v>1128980</v>
       </c>
       <c r="L412" s="14"/>
     </row>
-    <row r="413" spans="1:12">
+    <row r="413" spans="1:12" hidden="1">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -16981,7 +16997,7 @@
       <c r="K413" s="1"/>
       <c r="L413" s="1"/>
     </row>
-    <row r="414" spans="1:12" ht="26.4">
+    <row r="414" spans="1:12" ht="26.4" hidden="1">
       <c r="A414" s="1"/>
       <c r="B414" s="3" t="s">
         <v>12</v>
@@ -17017,7 +17033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="26.4">
+    <row r="415" spans="1:12" ht="26.4" hidden="1">
       <c r="A415" s="3" t="s">
         <v>11</v>
       </c>
@@ -17051,7 +17067,7 @@
       </c>
       <c r="L415" s="8"/>
     </row>
-    <row r="416" spans="1:12" ht="26.4">
+    <row r="416" spans="1:12" ht="26.4" hidden="1">
       <c r="A416" s="4">
         <v>1</v>
       </c>
@@ -17085,7 +17101,7 @@
       </c>
       <c r="L416" s="8"/>
     </row>
-    <row r="417" spans="1:12" ht="26.4">
+    <row r="417" spans="1:12" ht="26.4" hidden="1">
       <c r="A417" s="4">
         <v>2</v>
       </c>
@@ -17122,7 +17138,7 @@
       </c>
       <c r="L417" s="8"/>
     </row>
-    <row r="418" spans="1:12" ht="26.4">
+    <row r="418" spans="1:12" ht="26.4" hidden="1">
       <c r="A418" s="4">
         <v>3</v>
       </c>
@@ -17156,7 +17172,7 @@
       </c>
       <c r="L418" s="8"/>
     </row>
-    <row r="419" spans="1:12" ht="26.4">
+    <row r="419" spans="1:12" ht="26.4" hidden="1">
       <c r="A419" s="4">
         <v>4</v>
       </c>
@@ -17193,7 +17209,7 @@
       </c>
       <c r="L419" s="8"/>
     </row>
-    <row r="420" spans="1:12" ht="26.4">
+    <row r="420" spans="1:12" ht="26.4" hidden="1">
       <c r="A420" s="4">
         <v>5</v>
       </c>
@@ -17230,7 +17246,7 @@
       </c>
       <c r="L420" s="8"/>
     </row>
-    <row r="421" spans="1:12" ht="26.4">
+    <row r="421" spans="1:12" ht="26.4" hidden="1">
       <c r="A421" s="4">
         <v>6</v>
       </c>
@@ -17267,7 +17283,7 @@
       </c>
       <c r="L421" s="8"/>
     </row>
-    <row r="422" spans="1:12" ht="26.4">
+    <row r="422" spans="1:12" ht="26.4" hidden="1">
       <c r="A422" s="4">
         <v>7</v>
       </c>
@@ -17304,7 +17320,7 @@
       </c>
       <c r="L422" s="8"/>
     </row>
-    <row r="423" spans="1:12" ht="26.4">
+    <row r="423" spans="1:12" ht="26.4" hidden="1">
       <c r="A423" s="4">
         <v>8</v>
       </c>
@@ -17341,7 +17357,7 @@
       </c>
       <c r="L423" s="8"/>
     </row>
-    <row r="424" spans="1:12" ht="26.4">
+    <row r="424" spans="1:12" ht="26.4" hidden="1">
       <c r="A424" s="4">
         <v>9</v>
       </c>
@@ -17378,7 +17394,7 @@
       </c>
       <c r="L424" s="8"/>
     </row>
-    <row r="425" spans="1:12" ht="26.4">
+    <row r="425" spans="1:12" ht="26.4" hidden="1">
       <c r="A425" s="4">
         <v>10</v>
       </c>
@@ -17415,7 +17431,7 @@
       </c>
       <c r="L425" s="8"/>
     </row>
-    <row r="426" spans="1:12" ht="26.4">
+    <row r="426" spans="1:12" ht="26.4" hidden="1">
       <c r="A426" s="4">
         <v>11</v>
       </c>
@@ -17452,7 +17468,7 @@
       </c>
       <c r="L426" s="8"/>
     </row>
-    <row r="427" spans="1:12" ht="26.4">
+    <row r="427" spans="1:12" ht="26.4" hidden="1">
       <c r="A427" s="4">
         <v>12</v>
       </c>
@@ -17489,7 +17505,7 @@
       </c>
       <c r="L427" s="8"/>
     </row>
-    <row r="428" spans="1:12" ht="26.4">
+    <row r="428" spans="1:12" ht="26.4" hidden="1">
       <c r="A428" s="4">
         <v>13</v>
       </c>
@@ -17526,7 +17542,7 @@
       </c>
       <c r="L428" s="8"/>
     </row>
-    <row r="429" spans="1:12" ht="26.4">
+    <row r="429" spans="1:12" ht="26.4" hidden="1">
       <c r="A429" s="4">
         <v>14</v>
       </c>
@@ -17563,7 +17579,7 @@
       </c>
       <c r="L429" s="8"/>
     </row>
-    <row r="430" spans="1:12" ht="26.4">
+    <row r="430" spans="1:12" ht="26.4" hidden="1">
       <c r="A430" s="4">
         <v>15</v>
       </c>
@@ -17600,7 +17616,7 @@
       </c>
       <c r="L430" s="8"/>
     </row>
-    <row r="431" spans="1:12" ht="26.4">
+    <row r="431" spans="1:12" ht="26.4" hidden="1">
       <c r="A431" s="4">
         <v>16</v>
       </c>
@@ -17637,7 +17653,7 @@
       </c>
       <c r="L431" s="8"/>
     </row>
-    <row r="432" spans="1:12" ht="26.4">
+    <row r="432" spans="1:12" ht="26.4" hidden="1">
       <c r="A432" s="4">
         <v>17</v>
       </c>
@@ -17674,7 +17690,7 @@
       </c>
       <c r="L432" s="8"/>
     </row>
-    <row r="433" spans="1:12" ht="26.4">
+    <row r="433" spans="1:12" ht="26.4" hidden="1">
       <c r="A433" s="4">
         <v>18</v>
       </c>
@@ -17710,7 +17726,7 @@
         <v>29250</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="26.4">
+    <row r="434" spans="1:12" ht="26.4" hidden="1">
       <c r="A434" s="4">
         <v>19</v>
       </c>
@@ -17746,7 +17762,7 @@
       </c>
       <c r="L434" s="8"/>
     </row>
-    <row r="435" spans="1:12" ht="26.4">
+    <row r="435" spans="1:12" ht="26.4" hidden="1">
       <c r="A435" s="4">
         <v>20</v>
       </c>
@@ -17783,7 +17799,7 @@
       </c>
       <c r="L435" s="8"/>
     </row>
-    <row r="436" spans="1:12" ht="26.4">
+    <row r="436" spans="1:12" ht="26.4" hidden="1">
       <c r="A436" s="4">
         <v>21</v>
       </c>
@@ -17820,7 +17836,7 @@
       </c>
       <c r="L436" s="8"/>
     </row>
-    <row r="437" spans="1:12" ht="26.4">
+    <row r="437" spans="1:12" ht="26.4" hidden="1">
       <c r="A437" s="4">
         <v>22</v>
       </c>
@@ -17856,7 +17872,7 @@
       </c>
       <c r="L437" s="8"/>
     </row>
-    <row r="438" spans="1:12" ht="26.4">
+    <row r="438" spans="1:12" ht="26.4" hidden="1">
       <c r="A438" s="4">
         <v>23</v>
       </c>
@@ -17893,7 +17909,7 @@
       </c>
       <c r="L438" s="8"/>
     </row>
-    <row r="439" spans="1:12" ht="26.4">
+    <row r="439" spans="1:12" ht="26.4" hidden="1">
       <c r="A439" s="4">
         <v>24</v>
       </c>
@@ -17930,7 +17946,7 @@
       </c>
       <c r="L439" s="8"/>
     </row>
-    <row r="440" spans="1:12" ht="26.4">
+    <row r="440" spans="1:12" ht="26.4" hidden="1">
       <c r="A440" s="4">
         <v>25</v>
       </c>
@@ -17967,7 +17983,7 @@
       </c>
       <c r="L440" s="8"/>
     </row>
-    <row r="441" spans="1:12" ht="26.4">
+    <row r="441" spans="1:12" ht="26.4" hidden="1">
       <c r="A441" s="4">
         <v>26</v>
       </c>
@@ -18004,7 +18020,7 @@
       </c>
       <c r="L441" s="8"/>
     </row>
-    <row r="442" spans="1:12" ht="26.4">
+    <row r="442" spans="1:12" ht="26.4" hidden="1">
       <c r="A442" s="4">
         <v>27</v>
       </c>
@@ -18041,7 +18057,7 @@
       </c>
       <c r="L442" s="8"/>
     </row>
-    <row r="443" spans="1:12" ht="52.8">
+    <row r="443" spans="1:12" ht="52.8" hidden="1">
       <c r="A443" s="4">
         <v>28</v>
       </c>
@@ -18078,7 +18094,7 @@
       </c>
       <c r="L443" s="8"/>
     </row>
-    <row r="444" spans="1:12" ht="26.4">
+    <row r="444" spans="1:12" ht="26.4" hidden="1">
       <c r="A444" s="4">
         <v>29</v>
       </c>
@@ -18115,7 +18131,7 @@
       </c>
       <c r="L444" s="8"/>
     </row>
-    <row r="445" spans="1:12" ht="26.4">
+    <row r="445" spans="1:12" ht="26.4" hidden="1">
       <c r="A445" s="4">
         <v>30</v>
       </c>
@@ -18152,7 +18168,7 @@
       </c>
       <c r="L445" s="8"/>
     </row>
-    <row r="446" spans="1:12" ht="26.4">
+    <row r="446" spans="1:12" ht="26.4" hidden="1">
       <c r="A446" s="4">
         <v>31</v>
       </c>
@@ -18189,7 +18205,7 @@
       </c>
       <c r="L446" s="8"/>
     </row>
-    <row r="447" spans="1:12" ht="26.4">
+    <row r="447" spans="1:12" ht="26.4" hidden="1">
       <c r="A447" s="4">
         <v>32</v>
       </c>
@@ -18226,7 +18242,7 @@
       </c>
       <c r="L447" s="8"/>
     </row>
-    <row r="448" spans="1:12" ht="26.4">
+    <row r="448" spans="1:12" ht="26.4" hidden="1">
       <c r="A448" s="4">
         <v>33</v>
       </c>
@@ -18263,7 +18279,7 @@
       </c>
       <c r="L448" s="8"/>
     </row>
-    <row r="449" spans="1:12" ht="26.4">
+    <row r="449" spans="1:12" ht="26.4" hidden="1">
       <c r="A449" s="4">
         <v>34</v>
       </c>
@@ -18300,7 +18316,7 @@
       </c>
       <c r="L449" s="8"/>
     </row>
-    <row r="450" spans="1:12" ht="26.4">
+    <row r="450" spans="1:12" ht="26.4" hidden="1">
       <c r="A450" s="4">
         <v>35</v>
       </c>
@@ -18337,7 +18353,7 @@
       </c>
       <c r="L450" s="8"/>
     </row>
-    <row r="451" spans="1:12" ht="26.4">
+    <row r="451" spans="1:12" ht="26.4" hidden="1">
       <c r="A451" s="4">
         <v>36</v>
       </c>
@@ -18374,7 +18390,7 @@
       </c>
       <c r="L451" s="8"/>
     </row>
-    <row r="452" spans="1:12" ht="26.4">
+    <row r="452" spans="1:12" ht="26.4" hidden="1">
       <c r="A452" s="4">
         <v>37</v>
       </c>
@@ -18411,7 +18427,7 @@
       </c>
       <c r="L452" s="8"/>
     </row>
-    <row r="453" spans="1:12" ht="26.4">
+    <row r="453" spans="1:12" ht="26.4" hidden="1">
       <c r="A453" s="4">
         <v>38</v>
       </c>
@@ -18448,7 +18464,7 @@
       </c>
       <c r="L453" s="8"/>
     </row>
-    <row r="454" spans="1:12" ht="26.4">
+    <row r="454" spans="1:12" ht="26.4" hidden="1">
       <c r="A454" s="4">
         <v>39</v>
       </c>
@@ -18485,7 +18501,7 @@
       </c>
       <c r="L454" s="8"/>
     </row>
-    <row r="455" spans="1:12" ht="26.4">
+    <row r="455" spans="1:12" ht="26.4" hidden="1">
       <c r="A455" s="4">
         <v>40</v>
       </c>
@@ -18522,7 +18538,7 @@
       </c>
       <c r="L455" s="8"/>
     </row>
-    <row r="456" spans="1:12" ht="26.4">
+    <row r="456" spans="1:12" ht="26.4" hidden="1">
       <c r="A456" s="4">
         <v>41</v>
       </c>
@@ -18559,7 +18575,7 @@
       </c>
       <c r="L456" s="8"/>
     </row>
-    <row r="457" spans="1:12" ht="26.4">
+    <row r="457" spans="1:12" ht="26.4" hidden="1">
       <c r="A457" s="4">
         <v>42</v>
       </c>
@@ -18596,7 +18612,7 @@
       </c>
       <c r="L457" s="8"/>
     </row>
-    <row r="458" spans="1:12" ht="26.4">
+    <row r="458" spans="1:12" ht="26.4" hidden="1">
       <c r="A458" s="4">
         <v>43</v>
       </c>
@@ -18633,7 +18649,7 @@
       </c>
       <c r="L458" s="8"/>
     </row>
-    <row r="459" spans="1:12" ht="26.4">
+    <row r="459" spans="1:12" ht="26.4" hidden="1">
       <c r="A459" s="4">
         <v>44</v>
       </c>
@@ -18670,7 +18686,7 @@
       </c>
       <c r="L459" s="8"/>
     </row>
-    <row r="460" spans="1:12" ht="26.4">
+    <row r="460" spans="1:12" ht="26.4" hidden="1">
       <c r="A460" s="4">
         <v>45</v>
       </c>
@@ -18707,7 +18723,7 @@
       </c>
       <c r="L460" s="8"/>
     </row>
-    <row r="461" spans="1:12" ht="26.4">
+    <row r="461" spans="1:12" ht="26.4" hidden="1">
       <c r="A461" s="4">
         <v>46</v>
       </c>
@@ -18744,7 +18760,7 @@
       </c>
       <c r="L461" s="8"/>
     </row>
-    <row r="462" spans="1:12" ht="26.4">
+    <row r="462" spans="1:12" ht="26.4" hidden="1">
       <c r="A462" s="4">
         <v>47</v>
       </c>
@@ -18781,7 +18797,7 @@
       </c>
       <c r="L462" s="8"/>
     </row>
-    <row r="463" spans="1:12" ht="52.8">
+    <row r="463" spans="1:12" ht="52.8" hidden="1">
       <c r="A463" s="4">
         <v>48</v>
       </c>
@@ -18818,7 +18834,7 @@
       </c>
       <c r="L463" s="8"/>
     </row>
-    <row r="464" spans="1:12" ht="26.4">
+    <row r="464" spans="1:12" ht="26.4" hidden="1">
       <c r="A464" s="4">
         <v>49</v>
       </c>
@@ -18855,7 +18871,7 @@
       </c>
       <c r="L464" s="8"/>
     </row>
-    <row r="465" spans="1:12" ht="26.4">
+    <row r="465" spans="1:12" ht="26.4" hidden="1">
       <c r="A465" s="4">
         <v>50</v>
       </c>
@@ -18892,7 +18908,7 @@
       </c>
       <c r="L465" s="8"/>
     </row>
-    <row r="466" spans="1:12" ht="39.6">
+    <row r="466" spans="1:12" ht="39.6" hidden="1">
       <c r="A466" s="4">
         <v>51</v>
       </c>
@@ -18929,7 +18945,7 @@
       </c>
       <c r="L466" s="8"/>
     </row>
-    <row r="467" spans="1:12" ht="39.6">
+    <row r="467" spans="1:12" ht="39.6" hidden="1">
       <c r="A467" s="4">
         <v>52</v>
       </c>
@@ -18966,7 +18982,7 @@
       </c>
       <c r="L467" s="8"/>
     </row>
-    <row r="468" spans="1:12" ht="39.6">
+    <row r="468" spans="1:12" ht="39.6" hidden="1">
       <c r="A468" s="4">
         <v>53</v>
       </c>
@@ -19003,7 +19019,7 @@
       </c>
       <c r="L468" s="8"/>
     </row>
-    <row r="469" spans="1:12" ht="39.6">
+    <row r="469" spans="1:12" ht="39.6" hidden="1">
       <c r="A469" s="4">
         <v>54</v>
       </c>
@@ -19040,7 +19056,7 @@
       </c>
       <c r="L469" s="8"/>
     </row>
-    <row r="470" spans="1:12" ht="39.6">
+    <row r="470" spans="1:12" ht="39.6" hidden="1">
       <c r="A470" s="4">
         <v>55</v>
       </c>
@@ -19077,7 +19093,7 @@
       </c>
       <c r="L470" s="8"/>
     </row>
-    <row r="471" spans="1:12" ht="39.6">
+    <row r="471" spans="1:12" ht="39.6" hidden="1">
       <c r="A471" s="4">
         <v>56</v>
       </c>
@@ -19114,7 +19130,7 @@
       </c>
       <c r="L471" s="8"/>
     </row>
-    <row r="472" spans="1:12" ht="39.6">
+    <row r="472" spans="1:12" ht="39.6" hidden="1">
       <c r="A472" s="4">
         <v>57</v>
       </c>
@@ -19151,7 +19167,7 @@
       </c>
       <c r="L472" s="8"/>
     </row>
-    <row r="473" spans="1:12" ht="39.6">
+    <row r="473" spans="1:12" ht="39.6" hidden="1">
       <c r="A473" s="4">
         <v>58</v>
       </c>
@@ -19188,7 +19204,7 @@
       </c>
       <c r="L473" s="8"/>
     </row>
-    <row r="474" spans="1:12" ht="39.6">
+    <row r="474" spans="1:12" ht="39.6" hidden="1">
       <c r="A474" s="4">
         <v>59</v>
       </c>
@@ -19225,7 +19241,7 @@
       </c>
       <c r="L474" s="8"/>
     </row>
-    <row r="475" spans="1:12" ht="39.6">
+    <row r="475" spans="1:12" ht="39.6" hidden="1">
       <c r="A475" s="4">
         <v>60</v>
       </c>
@@ -19262,7 +19278,7 @@
       </c>
       <c r="L475" s="8"/>
     </row>
-    <row r="476" spans="1:12" ht="39.6">
+    <row r="476" spans="1:12" ht="39.6" hidden="1">
       <c r="A476" s="4">
         <v>61</v>
       </c>
@@ -19299,7 +19315,7 @@
       </c>
       <c r="L476" s="8"/>
     </row>
-    <row r="477" spans="1:12" ht="39.6">
+    <row r="477" spans="1:12" ht="39.6" hidden="1">
       <c r="A477" s="4">
         <v>62</v>
       </c>
@@ -19336,7 +19352,7 @@
       </c>
       <c r="L477" s="8"/>
     </row>
-    <row r="478" spans="1:12" ht="39.6">
+    <row r="478" spans="1:12" ht="39.6" hidden="1">
       <c r="A478" s="4">
         <v>63</v>
       </c>
@@ -19373,7 +19389,7 @@
       </c>
       <c r="L478" s="8"/>
     </row>
-    <row r="479" spans="1:12" ht="39.6">
+    <row r="479" spans="1:12" ht="39.6" hidden="1">
       <c r="A479" s="4">
         <v>64</v>
       </c>
@@ -19447,7 +19463,7 @@
       </c>
       <c r="L480" s="8"/>
     </row>
-    <row r="481" spans="1:12" ht="39.6">
+    <row r="481" spans="1:12" ht="39.6" hidden="1">
       <c r="A481" s="4">
         <v>66</v>
       </c>
@@ -19484,7 +19500,7 @@
       </c>
       <c r="L481" s="8"/>
     </row>
-    <row r="482" spans="1:12" ht="39.6">
+    <row r="482" spans="1:12" ht="39.6" hidden="1">
       <c r="A482" s="4">
         <v>67</v>
       </c>
@@ -19521,7 +19537,7 @@
       </c>
       <c r="L482" s="8"/>
     </row>
-    <row r="483" spans="1:12" ht="39.6">
+    <row r="483" spans="1:12" ht="39.6" hidden="1">
       <c r="A483" s="4">
         <v>68</v>
       </c>
@@ -19558,7 +19574,7 @@
       </c>
       <c r="L483" s="8"/>
     </row>
-    <row r="484" spans="1:12" ht="39.6">
+    <row r="484" spans="1:12" ht="39.6" hidden="1">
       <c r="A484" s="4">
         <v>69</v>
       </c>
@@ -19595,7 +19611,7 @@
       </c>
       <c r="L484" s="8"/>
     </row>
-    <row r="485" spans="1:12" ht="39.6">
+    <row r="485" spans="1:12" ht="39.6" hidden="1">
       <c r="A485" s="4">
         <v>70</v>
       </c>
@@ -19632,7 +19648,7 @@
       </c>
       <c r="L485" s="8"/>
     </row>
-    <row r="486" spans="1:12" ht="39.6">
+    <row r="486" spans="1:12" ht="39.6" hidden="1">
       <c r="A486" s="4">
         <v>71</v>
       </c>
@@ -19669,7 +19685,7 @@
       </c>
       <c r="L486" s="8"/>
     </row>
-    <row r="487" spans="1:12" ht="39.6">
+    <row r="487" spans="1:12" ht="39.6" hidden="1">
       <c r="A487" s="4">
         <v>72</v>
       </c>
@@ -19706,7 +19722,7 @@
       </c>
       <c r="L487" s="8"/>
     </row>
-    <row r="488" spans="1:12" ht="39.6">
+    <row r="488" spans="1:12" ht="39.6" hidden="1">
       <c r="A488" s="4">
         <v>73</v>
       </c>
@@ -19743,7 +19759,7 @@
       </c>
       <c r="L488" s="8"/>
     </row>
-    <row r="489" spans="1:12" ht="39.6">
+    <row r="489" spans="1:12" ht="39.6" hidden="1">
       <c r="A489" s="4">
         <v>74</v>
       </c>
@@ -19780,7 +19796,7 @@
       </c>
       <c r="L489" s="8"/>
     </row>
-    <row r="490" spans="1:12" ht="52.8">
+    <row r="490" spans="1:12" ht="52.8" hidden="1">
       <c r="A490" s="4">
         <v>75</v>
       </c>
@@ -19817,7 +19833,7 @@
       </c>
       <c r="L490" s="8"/>
     </row>
-    <row r="491" spans="1:12" ht="39.6">
+    <row r="491" spans="1:12" ht="39.6" hidden="1">
       <c r="A491" s="4">
         <v>76</v>
       </c>
@@ -19854,7 +19870,7 @@
       </c>
       <c r="L491" s="8"/>
     </row>
-    <row r="492" spans="1:12" ht="39.6">
+    <row r="492" spans="1:12" ht="39.6" hidden="1">
       <c r="A492" s="4">
         <v>77</v>
       </c>
@@ -19891,7 +19907,7 @@
       </c>
       <c r="L492" s="8"/>
     </row>
-    <row r="493" spans="1:12" ht="66">
+    <row r="493" spans="1:12" ht="66" hidden="1">
       <c r="A493" s="4">
         <v>78</v>
       </c>
@@ -19928,7 +19944,7 @@
       </c>
       <c r="L493" s="8"/>
     </row>
-    <row r="494" spans="1:12" ht="39.6">
+    <row r="494" spans="1:12" ht="39.6" hidden="1">
       <c r="A494" s="4">
         <v>79</v>
       </c>
@@ -20002,7 +20018,7 @@
       </c>
       <c r="L495" s="8"/>
     </row>
-    <row r="496" spans="1:12" ht="39.6">
+    <row r="496" spans="1:12" ht="39.6" hidden="1">
       <c r="A496" s="4">
         <v>81</v>
       </c>
@@ -20039,7 +20055,7 @@
       </c>
       <c r="L496" s="8"/>
     </row>
-    <row r="497" spans="1:12" ht="39.6">
+    <row r="497" spans="1:12" ht="39.6" hidden="1">
       <c r="A497" s="4">
         <v>82</v>
       </c>
@@ -20076,7 +20092,7 @@
       </c>
       <c r="L497" s="8"/>
     </row>
-    <row r="498" spans="1:12" ht="39.6">
+    <row r="498" spans="1:12" ht="39.6" hidden="1">
       <c r="A498" s="4">
         <v>83</v>
       </c>
@@ -20113,7 +20129,7 @@
       </c>
       <c r="L498" s="8"/>
     </row>
-    <row r="499" spans="1:12">
+    <row r="499" spans="1:12" hidden="1">
       <c r="A499" s="4">
         <v>84</v>
       </c>
@@ -20150,7 +20166,7 @@
       </c>
       <c r="L499" s="8"/>
     </row>
-    <row r="500" spans="1:12">
+    <row r="500" spans="1:12" hidden="1">
       <c r="A500" s="4">
         <v>85</v>
       </c>
@@ -20187,7 +20203,7 @@
       </c>
       <c r="L500" s="8"/>
     </row>
-    <row r="501" spans="1:12">
+    <row r="501" spans="1:12" hidden="1">
       <c r="A501" s="4">
         <v>86</v>
       </c>
@@ -20224,7 +20240,7 @@
       </c>
       <c r="L501" s="8"/>
     </row>
-    <row r="502" spans="1:12">
+    <row r="502" spans="1:12" hidden="1">
       <c r="A502" s="4">
         <v>87</v>
       </c>
@@ -20261,7 +20277,7 @@
       </c>
       <c r="L502" s="8"/>
     </row>
-    <row r="503" spans="1:12">
+    <row r="503" spans="1:12" hidden="1">
       <c r="A503" s="4">
         <v>88</v>
       </c>
@@ -20298,7 +20314,7 @@
       </c>
       <c r="L503" s="8"/>
     </row>
-    <row r="504" spans="1:12">
+    <row r="504" spans="1:12" hidden="1">
       <c r="A504" s="4">
         <v>89</v>
       </c>
@@ -20335,7 +20351,7 @@
       </c>
       <c r="L504" s="8"/>
     </row>
-    <row r="505" spans="1:12">
+    <row r="505" spans="1:12" hidden="1">
       <c r="A505" s="4">
         <v>90</v>
       </c>
@@ -20372,7 +20388,7 @@
       </c>
       <c r="L505" s="8"/>
     </row>
-    <row r="506" spans="1:12">
+    <row r="506" spans="1:12" hidden="1">
       <c r="A506" s="4">
         <v>91</v>
       </c>
@@ -20409,7 +20425,7 @@
       </c>
       <c r="L506" s="8"/>
     </row>
-    <row r="507" spans="1:12" ht="66">
+    <row r="507" spans="1:12" ht="66" hidden="1">
       <c r="A507" s="4">
         <v>92</v>
       </c>
@@ -20446,7 +20462,7 @@
       </c>
       <c r="L507" s="8"/>
     </row>
-    <row r="508" spans="1:12" ht="26.4">
+    <row r="508" spans="1:12" ht="26.4" hidden="1">
       <c r="A508" s="4">
         <v>93</v>
       </c>
@@ -20483,7 +20499,7 @@
       </c>
       <c r="L508" s="8"/>
     </row>
-    <row r="509" spans="1:12">
+    <row r="509" spans="1:12" hidden="1">
       <c r="A509" s="4">
         <v>94</v>
       </c>
@@ -20520,7 +20536,7 @@
       </c>
       <c r="L509" s="8"/>
     </row>
-    <row r="510" spans="1:12" s="10" customFormat="1" ht="39.6">
+    <row r="510" spans="1:12" s="10" customFormat="1" ht="39.6" hidden="1">
       <c r="A510" s="4">
         <v>95</v>
       </c>
@@ -20557,7 +20573,7 @@
       </c>
       <c r="L510" s="8"/>
     </row>
-    <row r="511" spans="1:12" s="10" customFormat="1" ht="28.8">
+    <row r="511" spans="1:12" s="10" customFormat="1" ht="28.8" hidden="1">
       <c r="A511" s="4">
         <v>96</v>
       </c>
@@ -20594,7 +20610,7 @@
       </c>
       <c r="L511" s="8"/>
     </row>
-    <row r="512" spans="1:12" s="10" customFormat="1" ht="28.8">
+    <row r="512" spans="1:12" s="10" customFormat="1" ht="28.8" hidden="1">
       <c r="A512" s="4">
         <v>97</v>
       </c>
@@ -20631,7 +20647,7 @@
       </c>
       <c r="L512" s="8"/>
     </row>
-    <row r="513" spans="1:12" s="10" customFormat="1" ht="28.8">
+    <row r="513" spans="1:12" s="10" customFormat="1" ht="28.8" hidden="1">
       <c r="A513" s="4">
         <v>98</v>
       </c>
@@ -20668,7 +20684,7 @@
       </c>
       <c r="L513" s="8"/>
     </row>
-    <row r="514" spans="1:12" s="10" customFormat="1" ht="52.8">
+    <row r="514" spans="1:12" s="10" customFormat="1" ht="52.8" hidden="1">
       <c r="A514" s="4">
         <v>99</v>
       </c>
@@ -20705,7 +20721,7 @@
       </c>
       <c r="L514" s="8"/>
     </row>
-    <row r="515" spans="1:12" s="10" customFormat="1" ht="28.8">
+    <row r="515" spans="1:12" s="10" customFormat="1" ht="28.8" hidden="1">
       <c r="A515" s="4">
         <v>102</v>
       </c>
@@ -20742,7 +20758,7 @@
       </c>
       <c r="L515" s="8"/>
     </row>
-    <row r="516" spans="1:12" s="10" customFormat="1" ht="28.8">
+    <row r="516" spans="1:12" s="10" customFormat="1" ht="28.8" hidden="1">
       <c r="A516" s="4">
         <v>103</v>
       </c>
@@ -20779,7 +20795,7 @@
       </c>
       <c r="L516" s="8"/>
     </row>
-    <row r="517" spans="1:12" s="10" customFormat="1" ht="28.8">
+    <row r="517" spans="1:12" s="10" customFormat="1" ht="28.8" hidden="1">
       <c r="A517" s="4">
         <v>104</v>
       </c>
@@ -20816,7 +20832,7 @@
       </c>
       <c r="L517" s="8"/>
     </row>
-    <row r="518" spans="1:12" s="10" customFormat="1" ht="28.8">
+    <row r="518" spans="1:12" s="10" customFormat="1" ht="28.8" hidden="1">
       <c r="A518" s="4">
         <v>105</v>
       </c>
@@ -20853,7 +20869,7 @@
       </c>
       <c r="L518" s="8"/>
     </row>
-    <row r="519" spans="1:12" s="10" customFormat="1" ht="26.4">
+    <row r="519" spans="1:12" s="10" customFormat="1" ht="26.4" hidden="1">
       <c r="A519" s="4">
         <v>106</v>
       </c>
@@ -20890,7 +20906,7 @@
       </c>
       <c r="L519" s="8"/>
     </row>
-    <row r="520" spans="1:12" s="10" customFormat="1" ht="26.4">
+    <row r="520" spans="1:12" s="10" customFormat="1" ht="26.4" hidden="1">
       <c r="A520" s="4">
         <v>107</v>
       </c>
@@ -20927,7 +20943,7 @@
       </c>
       <c r="L520" s="8"/>
     </row>
-    <row r="521" spans="1:12" s="10" customFormat="1" ht="26.4">
+    <row r="521" spans="1:12" s="10" customFormat="1" ht="26.4" hidden="1">
       <c r="A521" s="4">
         <v>108</v>
       </c>
@@ -20964,7 +20980,7 @@
       </c>
       <c r="L521" s="8"/>
     </row>
-    <row r="522" spans="1:12" s="10" customFormat="1" ht="26.4">
+    <row r="522" spans="1:12" s="10" customFormat="1" ht="26.4" hidden="1">
       <c r="A522" s="4">
         <v>109</v>
       </c>
@@ -21001,7 +21017,7 @@
       </c>
       <c r="L522" s="8"/>
     </row>
-    <row r="523" spans="1:12" s="10" customFormat="1">
+    <row r="523" spans="1:12" s="10" customFormat="1" hidden="1">
       <c r="A523" s="4">
         <v>110</v>
       </c>
@@ -21038,7 +21054,7 @@
       </c>
       <c r="L523" s="8"/>
     </row>
-    <row r="524" spans="1:12" s="10" customFormat="1">
+    <row r="524" spans="1:12" s="10" customFormat="1" hidden="1">
       <c r="A524" s="4">
         <v>111</v>
       </c>
@@ -21075,7 +21091,7 @@
       </c>
       <c r="L524" s="8"/>
     </row>
-    <row r="525" spans="1:12" s="10" customFormat="1">
+    <row r="525" spans="1:12" s="10" customFormat="1" hidden="1">
       <c r="A525" s="4">
         <v>112</v>
       </c>
@@ -21112,7 +21128,7 @@
       </c>
       <c r="L525" s="8"/>
     </row>
-    <row r="526" spans="1:12" s="10" customFormat="1">
+    <row r="526" spans="1:12" s="10" customFormat="1" hidden="1">
       <c r="A526" s="4">
         <v>113</v>
       </c>
@@ -21147,7 +21163,7 @@
       </c>
       <c r="L526" s="8"/>
     </row>
-    <row r="527" spans="1:12" s="10" customFormat="1">
+    <row r="527" spans="1:12" s="10" customFormat="1" hidden="1">
       <c r="A527" s="4">
         <v>114</v>
       </c>
@@ -21182,7 +21198,7 @@
       </c>
       <c r="L527" s="8"/>
     </row>
-    <row r="528" spans="1:12" s="10" customFormat="1">
+    <row r="528" spans="1:12" s="10" customFormat="1" hidden="1">
       <c r="A528" s="4">
         <v>115</v>
       </c>
@@ -21215,7 +21231,7 @@
       </c>
       <c r="L528" s="8"/>
     </row>
-    <row r="529" spans="1:12" s="10" customFormat="1">
+    <row r="529" spans="1:12" s="10" customFormat="1" hidden="1">
       <c r="A529" s="4">
         <v>116</v>
       </c>
@@ -21248,26 +21264,26 @@
       </c>
       <c r="L529" s="8"/>
     </row>
-    <row r="530" spans="1:12" ht="33.450000000000003" customHeight="1">
+    <row r="530" spans="1:12" ht="33.450000000000003" hidden="1" customHeight="1">
       <c r="A530" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B530" s="119"/>
-      <c r="C530" s="120"/>
-      <c r="D530" s="120"/>
-      <c r="E530" s="120"/>
-      <c r="F530" s="120"/>
-      <c r="G530" s="120"/>
-      <c r="H530" s="120"/>
-      <c r="I530" s="120"/>
-      <c r="J530" s="121"/>
+      <c r="B530" s="63"/>
+      <c r="C530" s="82"/>
+      <c r="D530" s="82"/>
+      <c r="E530" s="82"/>
+      <c r="F530" s="82"/>
+      <c r="G530" s="82"/>
+      <c r="H530" s="82"/>
+      <c r="I530" s="82"/>
+      <c r="J530" s="66"/>
       <c r="K530" s="12">
         <f>SUM(K415:K529)</f>
         <v>1372784.7</v>
       </c>
       <c r="L530" s="14"/>
     </row>
-    <row r="531" spans="1:12">
+    <row r="531" spans="1:12" hidden="1">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -21281,7 +21297,7 @@
       <c r="K531" s="1"/>
       <c r="L531" s="1"/>
     </row>
-    <row r="532" spans="1:12" ht="26.4">
+    <row r="532" spans="1:12" ht="26.4" hidden="1">
       <c r="A532" s="55"/>
       <c r="B532" s="3" t="s">
         <v>12</v>
@@ -21317,7 +21333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="533" spans="1:12" ht="66">
+    <row r="533" spans="1:12" ht="66" hidden="1">
       <c r="A533" s="3" t="s">
         <v>11</v>
       </c>
@@ -21354,7 +21370,7 @@
       </c>
       <c r="L533" s="8"/>
     </row>
-    <row r="534" spans="1:12" ht="26.4">
+    <row r="534" spans="1:12" ht="26.4" hidden="1">
       <c r="A534" s="4">
         <v>1</v>
       </c>
@@ -21391,7 +21407,7 @@
       </c>
       <c r="L534" s="8"/>
     </row>
-    <row r="535" spans="1:12" ht="26.4">
+    <row r="535" spans="1:12" ht="26.4" hidden="1">
       <c r="A535" s="4">
         <v>2</v>
       </c>
@@ -21428,7 +21444,7 @@
       </c>
       <c r="L535" s="8"/>
     </row>
-    <row r="536" spans="1:12" ht="26.4">
+    <row r="536" spans="1:12" ht="26.4" hidden="1">
       <c r="A536" s="4">
         <v>3</v>
       </c>
@@ -21465,7 +21481,7 @@
       </c>
       <c r="L536" s="8"/>
     </row>
-    <row r="537" spans="1:12" ht="26.4">
+    <row r="537" spans="1:12" ht="26.4" hidden="1">
       <c r="A537" s="4">
         <v>4</v>
       </c>
@@ -21502,7 +21518,7 @@
       </c>
       <c r="L537" s="8"/>
     </row>
-    <row r="538" spans="1:12" ht="26.4">
+    <row r="538" spans="1:12" ht="26.4" hidden="1">
       <c r="A538" s="4">
         <v>5</v>
       </c>
@@ -21539,7 +21555,7 @@
       </c>
       <c r="L538" s="8"/>
     </row>
-    <row r="539" spans="1:12" ht="26.4">
+    <row r="539" spans="1:12" ht="26.4" hidden="1">
       <c r="A539" s="4">
         <v>6</v>
       </c>
@@ -21576,7 +21592,7 @@
       </c>
       <c r="L539" s="8"/>
     </row>
-    <row r="540" spans="1:12" ht="26.4">
+    <row r="540" spans="1:12" ht="26.4" hidden="1">
       <c r="A540" s="4">
         <v>7</v>
       </c>
@@ -21613,7 +21629,7 @@
       </c>
       <c r="L540" s="8"/>
     </row>
-    <row r="541" spans="1:12" ht="26.4">
+    <row r="541" spans="1:12" ht="26.4" hidden="1">
       <c r="A541" s="4">
         <v>8</v>
       </c>
@@ -21650,7 +21666,7 @@
       </c>
       <c r="L541" s="8"/>
     </row>
-    <row r="542" spans="1:12" ht="26.4">
+    <row r="542" spans="1:12" ht="26.4" hidden="1">
       <c r="A542" s="4">
         <v>9</v>
       </c>
@@ -21687,7 +21703,7 @@
       </c>
       <c r="L542" s="8"/>
     </row>
-    <row r="543" spans="1:12" ht="26.4">
+    <row r="543" spans="1:12" ht="26.4" hidden="1">
       <c r="A543" s="4">
         <v>10</v>
       </c>
@@ -21724,7 +21740,7 @@
       </c>
       <c r="L543" s="8"/>
     </row>
-    <row r="544" spans="1:12" ht="26.4">
+    <row r="544" spans="1:12" ht="26.4" hidden="1">
       <c r="A544" s="4">
         <v>11</v>
       </c>
@@ -21761,7 +21777,7 @@
       </c>
       <c r="L544" s="8"/>
     </row>
-    <row r="545" spans="1:12" ht="26.4">
+    <row r="545" spans="1:12" ht="26.4" hidden="1">
       <c r="A545" s="4">
         <v>12</v>
       </c>
@@ -21798,7 +21814,7 @@
       </c>
       <c r="L545" s="8"/>
     </row>
-    <row r="546" spans="1:12" ht="27.6">
+    <row r="546" spans="1:12" ht="27.6" hidden="1">
       <c r="A546" s="4">
         <v>13</v>
       </c>
@@ -21837,7 +21853,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="547" spans="1:12" ht="26.4">
+    <row r="547" spans="1:12" ht="26.4" hidden="1">
       <c r="A547" s="4">
         <v>14</v>
       </c>
@@ -21874,7 +21890,7 @@
       </c>
       <c r="L547" s="8"/>
     </row>
-    <row r="548" spans="1:12" ht="26.4">
+    <row r="548" spans="1:12" ht="26.4" hidden="1">
       <c r="A548" s="4">
         <v>15</v>
       </c>
@@ -21911,7 +21927,7 @@
       </c>
       <c r="L548" s="8"/>
     </row>
-    <row r="549" spans="1:12" ht="27.6">
+    <row r="549" spans="1:12" ht="27.6" hidden="1">
       <c r="A549" s="4">
         <v>16</v>
       </c>
@@ -21950,7 +21966,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="550" spans="1:12" ht="27.6">
+    <row r="550" spans="1:12" ht="27.6" hidden="1">
       <c r="A550" s="4">
         <v>17</v>
       </c>
@@ -21989,7 +22005,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="551" spans="1:12" ht="26.4">
+    <row r="551" spans="1:12" ht="26.4" hidden="1">
       <c r="A551" s="4">
         <v>18</v>
       </c>
@@ -22026,7 +22042,7 @@
       </c>
       <c r="L551" s="9"/>
     </row>
-    <row r="552" spans="1:12" ht="66">
+    <row r="552" spans="1:12" ht="66" hidden="1">
       <c r="A552" s="4">
         <v>19</v>
       </c>
@@ -22062,7 +22078,7 @@
       </c>
       <c r="L552" s="8"/>
     </row>
-    <row r="553" spans="1:12" ht="26.4">
+    <row r="553" spans="1:12" ht="26.4" hidden="1">
       <c r="A553" s="4">
         <v>20</v>
       </c>
@@ -22099,7 +22115,7 @@
       </c>
       <c r="L553" s="8"/>
     </row>
-    <row r="554" spans="1:12" ht="26.4">
+    <row r="554" spans="1:12" ht="26.4" hidden="1">
       <c r="A554" s="4">
         <v>21</v>
       </c>
@@ -22136,7 +22152,7 @@
       </c>
       <c r="L554" s="8"/>
     </row>
-    <row r="555" spans="1:12" ht="26.4">
+    <row r="555" spans="1:12" ht="26.4" hidden="1">
       <c r="A555" s="4">
         <v>22</v>
       </c>
@@ -22172,7 +22188,7 @@
       </c>
       <c r="L555" s="8"/>
     </row>
-    <row r="556" spans="1:12" ht="26.4">
+    <row r="556" spans="1:12" ht="26.4" hidden="1">
       <c r="A556" s="4">
         <v>23</v>
       </c>
@@ -22209,7 +22225,7 @@
       </c>
       <c r="L556" s="8"/>
     </row>
-    <row r="557" spans="1:12" ht="26.4">
+    <row r="557" spans="1:12" ht="26.4" hidden="1">
       <c r="A557" s="4">
         <v>24</v>
       </c>
@@ -22246,7 +22262,7 @@
       </c>
       <c r="L557" s="8"/>
     </row>
-    <row r="558" spans="1:12" ht="36" customHeight="1">
+    <row r="558" spans="1:12" ht="36" hidden="1" customHeight="1">
       <c r="A558" s="4">
         <v>25</v>
       </c>
@@ -22283,7 +22299,7 @@
       </c>
       <c r="L558" s="8"/>
     </row>
-    <row r="559" spans="1:12" ht="26.4">
+    <row r="559" spans="1:12" ht="26.4" hidden="1">
       <c r="A559" s="4">
         <v>26</v>
       </c>
@@ -22320,7 +22336,7 @@
       </c>
       <c r="L559" s="8"/>
     </row>
-    <row r="560" spans="1:12" ht="26.4">
+    <row r="560" spans="1:12" ht="26.4" hidden="1">
       <c r="A560" s="4">
         <v>27</v>
       </c>
@@ -22357,7 +22373,7 @@
       </c>
       <c r="L560" s="8"/>
     </row>
-    <row r="561" spans="1:12" ht="26.4">
+    <row r="561" spans="1:12" ht="26.4" hidden="1">
       <c r="A561" s="4">
         <v>28</v>
       </c>
@@ -22394,7 +22410,7 @@
       </c>
       <c r="L561" s="8"/>
     </row>
-    <row r="562" spans="1:12" ht="26.4">
+    <row r="562" spans="1:12" ht="26.4" hidden="1">
       <c r="A562" s="4">
         <v>29</v>
       </c>
@@ -22431,7 +22447,7 @@
       </c>
       <c r="L562" s="8"/>
     </row>
-    <row r="563" spans="1:12" ht="26.4">
+    <row r="563" spans="1:12" ht="26.4" hidden="1">
       <c r="A563" s="4">
         <v>30</v>
       </c>
@@ -22468,7 +22484,7 @@
       </c>
       <c r="L563" s="8"/>
     </row>
-    <row r="564" spans="1:12" ht="26.4">
+    <row r="564" spans="1:12" ht="26.4" hidden="1">
       <c r="A564" s="4">
         <v>31</v>
       </c>
@@ -22505,7 +22521,7 @@
       </c>
       <c r="L564" s="8"/>
     </row>
-    <row r="565" spans="1:12" ht="26.4">
+    <row r="565" spans="1:12" ht="26.4" hidden="1">
       <c r="A565" s="4">
         <v>32</v>
       </c>
@@ -22542,7 +22558,7 @@
       </c>
       <c r="L565" s="8"/>
     </row>
-    <row r="566" spans="1:12" ht="66">
+    <row r="566" spans="1:12" ht="66" hidden="1">
       <c r="A566" s="4">
         <v>33</v>
       </c>
@@ -22579,7 +22595,7 @@
       </c>
       <c r="L566" s="8"/>
     </row>
-    <row r="567" spans="1:12" ht="26.4">
+    <row r="567" spans="1:12" ht="26.4" hidden="1">
       <c r="A567" s="4">
         <v>34</v>
       </c>
@@ -22616,7 +22632,7 @@
       </c>
       <c r="L567" s="8"/>
     </row>
-    <row r="568" spans="1:12" ht="39.6">
+    <row r="568" spans="1:12" ht="39.6" hidden="1">
       <c r="A568" s="4">
         <v>35</v>
       </c>
@@ -22653,7 +22669,7 @@
       </c>
       <c r="L568" s="8"/>
     </row>
-    <row r="569" spans="1:12" ht="39.6">
+    <row r="569" spans="1:12" ht="39.6" hidden="1">
       <c r="A569" s="4">
         <v>36</v>
       </c>
@@ -22690,7 +22706,7 @@
       </c>
       <c r="L569" s="8"/>
     </row>
-    <row r="570" spans="1:12" ht="39.6">
+    <row r="570" spans="1:12" ht="39.6" hidden="1">
       <c r="A570" s="4">
         <v>37</v>
       </c>
@@ -22727,7 +22743,7 @@
       </c>
       <c r="L570" s="8"/>
     </row>
-    <row r="571" spans="1:12" ht="39.6">
+    <row r="571" spans="1:12" ht="39.6" hidden="1">
       <c r="A571" s="4">
         <v>38</v>
       </c>
@@ -22801,7 +22817,7 @@
       </c>
       <c r="L572" s="8"/>
     </row>
-    <row r="573" spans="1:12" ht="39.6">
+    <row r="573" spans="1:12" ht="39.6" hidden="1">
       <c r="A573" s="4">
         <v>40</v>
       </c>
@@ -22838,7 +22854,7 @@
       </c>
       <c r="L573" s="8"/>
     </row>
-    <row r="574" spans="1:12" ht="39.6">
+    <row r="574" spans="1:12" ht="39.6" hidden="1">
       <c r="A574" s="4">
         <v>41</v>
       </c>
@@ -22912,7 +22928,7 @@
       </c>
       <c r="L575" s="8"/>
     </row>
-    <row r="576" spans="1:12" ht="39.6">
+    <row r="576" spans="1:12" ht="39.6" hidden="1">
       <c r="A576" s="4">
         <v>43</v>
       </c>
@@ -22949,7 +22965,7 @@
       </c>
       <c r="L576" s="8"/>
     </row>
-    <row r="577" spans="1:12" ht="26.4">
+    <row r="577" spans="1:12" ht="26.4" hidden="1">
       <c r="A577" s="4">
         <v>44</v>
       </c>
@@ -22988,7 +23004,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="578" spans="1:12" ht="26.4">
+    <row r="578" spans="1:12" ht="26.4" hidden="1">
       <c r="A578" s="4">
         <v>45</v>
       </c>
@@ -23027,7 +23043,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="579" spans="1:12" ht="69">
+    <row r="579" spans="1:12" ht="69" hidden="1">
       <c r="A579" s="4">
         <v>46</v>
       </c>
@@ -23066,7 +23082,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="580" spans="1:12">
+    <row r="580" spans="1:12" hidden="1">
       <c r="A580" s="4">
         <v>47</v>
       </c>
@@ -23103,7 +23119,7 @@
       </c>
       <c r="L580" s="8"/>
     </row>
-    <row r="581" spans="1:12">
+    <row r="581" spans="1:12" hidden="1">
       <c r="A581" s="4">
         <v>48</v>
       </c>
@@ -23140,7 +23156,7 @@
       </c>
       <c r="L581" s="8"/>
     </row>
-    <row r="582" spans="1:12">
+    <row r="582" spans="1:12" hidden="1">
       <c r="A582" s="4">
         <v>49</v>
       </c>
@@ -23177,7 +23193,7 @@
       </c>
       <c r="L582" s="8"/>
     </row>
-    <row r="583" spans="1:12" ht="26.4">
+    <row r="583" spans="1:12" ht="26.4" hidden="1">
       <c r="A583" s="4">
         <v>50</v>
       </c>
@@ -23214,7 +23230,7 @@
       </c>
       <c r="L583" s="8"/>
     </row>
-    <row r="584" spans="1:12" ht="26.4">
+    <row r="584" spans="1:12" ht="26.4" hidden="1">
       <c r="A584" s="4">
         <v>51</v>
       </c>
@@ -23251,7 +23267,7 @@
       </c>
       <c r="L584" s="8"/>
     </row>
-    <row r="585" spans="1:12">
+    <row r="585" spans="1:12" hidden="1">
       <c r="A585" s="4">
         <v>52</v>
       </c>
@@ -23288,7 +23304,7 @@
       </c>
       <c r="L585" s="8"/>
     </row>
-    <row r="586" spans="1:12">
+    <row r="586" spans="1:12" hidden="1">
       <c r="A586" s="4">
         <v>53</v>
       </c>
@@ -23325,7 +23341,7 @@
       </c>
       <c r="L586" s="8"/>
     </row>
-    <row r="587" spans="1:12" ht="26.4">
+    <row r="587" spans="1:12" ht="26.4" hidden="1">
       <c r="A587" s="4">
         <v>54</v>
       </c>
@@ -23362,7 +23378,7 @@
       </c>
       <c r="L587" s="8"/>
     </row>
-    <row r="588" spans="1:12">
+    <row r="588" spans="1:12" hidden="1">
       <c r="A588" s="4">
         <v>55</v>
       </c>
@@ -23399,7 +23415,7 @@
       </c>
       <c r="L588" s="8"/>
     </row>
-    <row r="589" spans="1:12" ht="26.4">
+    <row r="589" spans="1:12" ht="26.4" hidden="1">
       <c r="A589" s="4">
         <v>56</v>
       </c>
@@ -23436,7 +23452,7 @@
       </c>
       <c r="L589" s="8"/>
     </row>
-    <row r="590" spans="1:12">
+    <row r="590" spans="1:12" hidden="1">
       <c r="A590" s="4">
         <v>57</v>
       </c>
@@ -23473,7 +23489,7 @@
       </c>
       <c r="L590" s="8"/>
     </row>
-    <row r="591" spans="1:12" ht="27.6">
+    <row r="591" spans="1:12" ht="27.6" hidden="1">
       <c r="A591" s="4">
         <v>58</v>
       </c>
@@ -23512,7 +23528,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="592" spans="1:12">
+    <row r="592" spans="1:12" hidden="1">
       <c r="A592" s="4">
         <v>59</v>
       </c>
@@ -23549,7 +23565,7 @@
       </c>
       <c r="L592" s="8"/>
     </row>
-    <row r="593" spans="1:12" ht="26.4">
+    <row r="593" spans="1:12" ht="26.4" hidden="1">
       <c r="A593" s="4">
         <v>60</v>
       </c>
@@ -23586,7 +23602,7 @@
       </c>
       <c r="L593" s="8"/>
     </row>
-    <row r="594" spans="1:12" ht="26.4">
+    <row r="594" spans="1:12" ht="26.4" hidden="1">
       <c r="A594" s="4">
         <v>61</v>
       </c>
@@ -23623,7 +23639,7 @@
       </c>
       <c r="L594" s="8"/>
     </row>
-    <row r="595" spans="1:12" ht="26.4">
+    <row r="595" spans="1:12" ht="26.4" hidden="1">
       <c r="A595" s="4">
         <v>62</v>
       </c>
@@ -23660,7 +23676,7 @@
       </c>
       <c r="L595" s="8"/>
     </row>
-    <row r="596" spans="1:12" ht="26.4">
+    <row r="596" spans="1:12" ht="26.4" hidden="1">
       <c r="A596" s="4">
         <v>63</v>
       </c>
@@ -23697,7 +23713,7 @@
       </c>
       <c r="L596" s="8"/>
     </row>
-    <row r="597" spans="1:12" ht="26.4">
+    <row r="597" spans="1:12" ht="26.4" hidden="1">
       <c r="A597" s="4">
         <v>64</v>
       </c>
@@ -23734,7 +23750,7 @@
       </c>
       <c r="L597" s="8"/>
     </row>
-    <row r="598" spans="1:12" ht="26.4">
+    <row r="598" spans="1:12" ht="26.4" hidden="1">
       <c r="A598" s="4">
         <v>65</v>
       </c>
@@ -23771,7 +23787,7 @@
       </c>
       <c r="L598" s="8"/>
     </row>
-    <row r="599" spans="1:12" ht="26.4">
+    <row r="599" spans="1:12" ht="26.4" hidden="1">
       <c r="A599" s="4">
         <v>66</v>
       </c>
@@ -23808,7 +23824,7 @@
       </c>
       <c r="L599" s="8"/>
     </row>
-    <row r="600" spans="1:12" ht="26.4">
+    <row r="600" spans="1:12" ht="26.4" hidden="1">
       <c r="A600" s="4">
         <v>67</v>
       </c>
@@ -23845,7 +23861,7 @@
       </c>
       <c r="L600" s="8"/>
     </row>
-    <row r="601" spans="1:12" ht="26.4">
+    <row r="601" spans="1:12" ht="26.4" hidden="1">
       <c r="A601" s="4">
         <v>68</v>
       </c>
@@ -23882,7 +23898,7 @@
       </c>
       <c r="L601" s="8"/>
     </row>
-    <row r="602" spans="1:12" ht="26.4">
+    <row r="602" spans="1:12" ht="26.4" hidden="1">
       <c r="A602" s="4">
         <v>69</v>
       </c>
@@ -23919,7 +23935,7 @@
       </c>
       <c r="L602" s="8"/>
     </row>
-    <row r="603" spans="1:12">
+    <row r="603" spans="1:12" hidden="1">
       <c r="A603" s="4">
         <v>70</v>
       </c>
@@ -23956,7 +23972,7 @@
       </c>
       <c r="L603" s="8"/>
     </row>
-    <row r="604" spans="1:12">
+    <row r="604" spans="1:12" hidden="1">
       <c r="A604" s="4">
         <v>71</v>
       </c>
@@ -23993,7 +24009,7 @@
       </c>
       <c r="L604" s="8"/>
     </row>
-    <row r="605" spans="1:12" ht="26.4">
+    <row r="605" spans="1:12" ht="26.4" hidden="1">
       <c r="A605" s="4">
         <v>72</v>
       </c>
@@ -24030,7 +24046,7 @@
       </c>
       <c r="L605" s="8"/>
     </row>
-    <row r="606" spans="1:12" ht="26.4">
+    <row r="606" spans="1:12" ht="26.4" hidden="1">
       <c r="A606" s="4">
         <v>73</v>
       </c>
@@ -24067,7 +24083,7 @@
       </c>
       <c r="L606" s="8"/>
     </row>
-    <row r="607" spans="1:12" ht="26.4">
+    <row r="607" spans="1:12" ht="26.4" hidden="1">
       <c r="A607" s="4">
         <v>74</v>
       </c>
@@ -24104,7 +24120,7 @@
       </c>
       <c r="L607" s="8"/>
     </row>
-    <row r="608" spans="1:12">
+    <row r="608" spans="1:12" hidden="1">
       <c r="A608" s="4">
         <v>75</v>
       </c>
@@ -24141,7 +24157,7 @@
       </c>
       <c r="L608" s="8"/>
     </row>
-    <row r="609" spans="1:12" ht="26.4">
+    <row r="609" spans="1:12" ht="26.4" hidden="1">
       <c r="A609" s="4">
         <v>76</v>
       </c>
@@ -24178,7 +24194,7 @@
       </c>
       <c r="L609" s="8"/>
     </row>
-    <row r="610" spans="1:12">
+    <row r="610" spans="1:12" hidden="1">
       <c r="A610" s="4">
         <v>77</v>
       </c>
@@ -24215,7 +24231,7 @@
       </c>
       <c r="L610" s="8"/>
     </row>
-    <row r="611" spans="1:12">
+    <row r="611" spans="1:12" hidden="1">
       <c r="A611" s="4">
         <v>78</v>
       </c>
@@ -24252,7 +24268,7 @@
       </c>
       <c r="L611" s="8"/>
     </row>
-    <row r="612" spans="1:12" ht="26.4">
+    <row r="612" spans="1:12" ht="26.4" hidden="1">
       <c r="A612" s="4">
         <v>79</v>
       </c>
@@ -24289,7 +24305,7 @@
       </c>
       <c r="L612" s="8"/>
     </row>
-    <row r="613" spans="1:12" ht="26.4">
+    <row r="613" spans="1:12" ht="26.4" hidden="1">
       <c r="A613" s="4">
         <v>80</v>
       </c>
@@ -24328,7 +24344,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="614" spans="1:12" ht="26.4">
+    <row r="614" spans="1:12" ht="26.4" hidden="1">
       <c r="A614" s="4">
         <v>81</v>
       </c>
@@ -24367,7 +24383,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="615" spans="1:12" ht="26.4">
+    <row r="615" spans="1:12" ht="26.4" hidden="1">
       <c r="A615" s="4">
         <v>82</v>
       </c>
@@ -24406,7 +24422,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="616" spans="1:12" ht="26.4">
+    <row r="616" spans="1:12" ht="26.4" hidden="1">
       <c r="A616" s="4">
         <v>83</v>
       </c>
@@ -24445,7 +24461,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="617" spans="1:12" ht="26.4">
+    <row r="617" spans="1:12" ht="26.4" hidden="1">
       <c r="A617" s="4">
         <v>84</v>
       </c>
@@ -24484,7 +24500,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="618" spans="1:12" ht="26.4">
+    <row r="618" spans="1:12" ht="26.4" hidden="1">
       <c r="A618" s="4">
         <v>85</v>
       </c>
@@ -24523,7 +24539,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="619" spans="1:12" ht="26.4">
+    <row r="619" spans="1:12" ht="26.4" hidden="1">
       <c r="A619" s="4">
         <v>86</v>
       </c>
@@ -24562,7 +24578,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="620" spans="1:12" ht="15.6">
+    <row r="620" spans="1:12" ht="15.6" hidden="1">
       <c r="A620" s="4">
         <v>87</v>
       </c>
@@ -24599,7 +24615,7 @@
       </c>
       <c r="L620" s="8"/>
     </row>
-    <row r="621" spans="1:12" ht="15.6">
+    <row r="621" spans="1:12" ht="15.6" hidden="1">
       <c r="A621" s="4">
         <v>88</v>
       </c>
@@ -24636,7 +24652,7 @@
       </c>
       <c r="L621" s="8"/>
     </row>
-    <row r="622" spans="1:12" ht="15.6">
+    <row r="622" spans="1:12" ht="15.6" hidden="1">
       <c r="A622" s="4">
         <v>89</v>
       </c>
@@ -24673,7 +24689,7 @@
       </c>
       <c r="L622" s="8"/>
     </row>
-    <row r="623" spans="1:12" ht="15.6">
+    <row r="623" spans="1:12" ht="15.6" hidden="1">
       <c r="A623" s="4">
         <v>90</v>
       </c>
@@ -24710,7 +24726,7 @@
       </c>
       <c r="L623" s="8"/>
     </row>
-    <row r="624" spans="1:12" ht="15.6">
+    <row r="624" spans="1:12" ht="15.6" hidden="1">
       <c r="A624" s="4">
         <v>91</v>
       </c>
@@ -24747,7 +24763,7 @@
       </c>
       <c r="L624" s="8"/>
     </row>
-    <row r="625" spans="1:12" ht="15.6">
+    <row r="625" spans="1:12" ht="15.6" hidden="1">
       <c r="A625" s="4">
         <v>92</v>
       </c>
@@ -24784,7 +24800,7 @@
       </c>
       <c r="L625" s="8"/>
     </row>
-    <row r="626" spans="1:12">
+    <row r="626" spans="1:12" hidden="1">
       <c r="A626" s="4">
         <v>93</v>
       </c>
@@ -24817,7 +24833,7 @@
       </c>
       <c r="L626" s="8"/>
     </row>
-    <row r="627" spans="1:12">
+    <row r="627" spans="1:12" hidden="1">
       <c r="A627" s="4">
         <v>94</v>
       </c>
@@ -24850,7 +24866,7 @@
       </c>
       <c r="L627" s="8"/>
     </row>
-    <row r="628" spans="1:12" ht="42.6" customHeight="1">
+    <row r="628" spans="1:12" ht="42.6" hidden="1" customHeight="1">
       <c r="A628" s="35" t="s">
         <v>24</v>
       </c>
@@ -24873,16 +24889,32 @@
       <c r="A630" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B76:J76"/>
-    <mergeCell ref="B26:J26"/>
+  <autoFilter ref="F3:I628">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1.13 Санузел для девочек 15,0"/>
+        <filter val="1.15 Санузел для мальчиков 15,0"/>
+        <filter val="2.06 Универсальное помещение с возможностью проведения занятий во внеурочное время в том числе для групп продленного дня 63,2"/>
+        <filter val="2.14 Санузел для мальчиков 8,1"/>
+        <filter val="2.24 Санузел для девочек 15,0"/>
+        <filter val="2.25 Санузел для мальчиков 15,0"/>
+        <filter val="3.10 Санузел для девочек 15,1"/>
+        <filter val="3.11 Санузел для мальчиков 15,1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Штукатурка стен сухими смесями с установкой маяков с предварительной огрунтовкой / толщ. от 16,5 мм до 21 мм"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="1">
     <mergeCell ref="B628:J628"/>
-    <mergeCell ref="B530:J530"/>
-    <mergeCell ref="B412:J412"/>
-    <mergeCell ref="B307:J307"/>
-    <mergeCell ref="B172:J172"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="F3:H577">
+    <cfRule type="uniqueValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E310:E400 E403:E409 E411 E415:E505 E508:E528 D310:D411 D417 D268:D306 D419:D529 C515:C529 C287:C288 C310:C402 C415:C507 B415:B529 B79:D171 B310:B411 B268:B306 B29:E75 G69 G74:G75 F29:G51 G79:G141 G143:G169 G171 F310:G409 G411 G529 G268:G306 F415:G527 F53:G68 E79:F169 E266:F306 F70:F73">
       <formula1>#REF!</formula1>
